--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE122"/>
+  <dimension ref="A1:AE121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 2764-2023</t>
+          <t>A 417-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44944</v>
+        <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,153 +871,153 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2764-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Ask
 Vårstarr</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 417-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 29724-2022</t>
+          <t>A 25330-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44755</v>
+        <v>46176</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>11.8</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1080,10 +1080,10 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1092,148 +1092,148 @@
         </is>
       </c>
       <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 25330-2026 artfynd.xlsx", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 25330-2026 karta.png", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 25330-2026 georefererad karta.tif", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 25330-2026 karta knärot.png", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 25330-2026 FSC-klagomål.docx", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 25330-2026 FSC-klagomål mail.docx", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 25330-2026 tillsynsbegäran.docx", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 25330-2026 tillsynsbegäran mail.docx", "A 25330-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 29724-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44755</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29724-2022 artfynd.xlsx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29724-2022 karta.png", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29724-2022 georefererad karta.tif", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 29724-2022 karta knärot.png", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29724-2022 FSC-klagomål.docx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29724-2022 FSC-klagomål mail.docx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29724-2022 tillsynsbegäran.docx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29724-2022 tillsynsbegäran mail.docx", "A 29724-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 25330-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Flagellkvastmossa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 25330-2026 artfynd.xlsx", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 25330-2026 karta.png", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 25330-2026 georefererad karta.tif", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 25330-2026 karta knärot.png", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 25330-2026 FSC-klagomål.docx", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 25330-2026 FSC-klagomål mail.docx", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 25330-2026 tillsynsbegäran.docx", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 25330-2026 tillsynsbegäran mail.docx", "A 25330-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44690</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48904-2021</t>
+          <t>A 29819-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1353,14 +1353,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44453</v>
+        <v>45825</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1413,42 +1413,46 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 48904-2021 artfynd.xlsx", "A 48904-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 48904-2021 karta.png", "A 48904-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 48904-2021 georefererad karta.tif", "A 48904-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 48904-2021 FSC-klagomål.docx", "A 48904-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 48904-2021 FSC-klagomål mail.docx", "A 48904-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 48904-2021 tillsynsbegäran.docx", "A 48904-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 48904-2021 tillsynsbegäran mail.docx", "A 48904-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 29819-2025</t>
+          <t>A 56101-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1462,10 +1466,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45825</v>
+        <v>45973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1478,13 +1482,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1514,50 +1518,46 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 56101-2025</t>
+          <t>A 31382-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45973</v>
+        <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1627,35 +1627,35 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
         <v>44944</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 31382-2026</t>
+          <t>A 6870-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46219</v>
+        <v>44602</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1827,52 +1827,20 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
+      <c r="V13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6870-2022</t>
+          <t>A 25943-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1882,14 +1850,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44602</v>
+        <v>44734</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1902,7 +1870,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1945,7 +1913,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25943-2022</t>
+          <t>A 6871-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1955,14 +1923,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44734</v>
+        <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1975,7 +1943,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2018,7 +1986,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6871-2022</t>
+          <t>A 6800-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2035,7 +2003,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2048,7 +2016,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2091,7 +2059,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6800-2022</t>
+          <t>A 10328-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2105,10 +2073,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44602</v>
+        <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2121,7 +2089,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2181,7 +2149,7 @@
         <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2237,7 +2205,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10328-2022</t>
+          <t>A 36402-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2251,10 +2219,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44623</v>
+        <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2266,8 +2234,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2310,7 +2283,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 36402-2022</t>
+          <t>A 64871-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2324,10 +2297,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44804</v>
+        <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2339,13 +2312,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2388,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 64871-2021</t>
+          <t>A 23080-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2402,10 +2370,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44512</v>
+        <v>44715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2418,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2461,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23080-2022</t>
+          <t>A 65112-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2475,10 +2443,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44715</v>
+        <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2491,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2534,7 +2502,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 65112-2021</t>
+          <t>A 36404-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2548,10 +2516,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44515</v>
+        <v>44804</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2561,6 +2529,11 @@
       <c r="G23" t="inlineStr">
         <is>
           <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -2607,7 +2580,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36404-2022</t>
+          <t>A 1882-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2621,10 +2594,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44804</v>
+        <v>44574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2636,13 +2609,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2685,7 +2653,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1882-2022</t>
+          <t>A 46707-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2699,10 +2667,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44574</v>
+        <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2715,7 +2683,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2758,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 46707-2022</t>
+          <t>A 495-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2772,10 +2740,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44851</v>
+        <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2787,8 +2755,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2831,7 +2804,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 495-2022</t>
+          <t>A 496-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2848,7 +2821,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2866,7 +2839,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2909,7 +2882,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 496-2022</t>
+          <t>A 65095-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2923,10 +2896,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44566</v>
+        <v>44515</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2938,13 +2911,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2987,7 +2955,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 65095-2021</t>
+          <t>A 61986-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3001,10 +2969,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44515</v>
+        <v>44502</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3016,8 +2984,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3060,7 +3033,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 61986-2021</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3074,10 +3047,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44502</v>
+        <v>44922</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3089,13 +3062,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3138,7 +3106,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3152,10 +3120,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45229</v>
+        <v>44715</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3168,7 +3136,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3211,7 +3179,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3225,10 +3193,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44515</v>
+        <v>45107</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3284,7 +3252,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3298,10 +3266,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45401</v>
+        <v>45191</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3314,7 +3282,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3357,7 +3325,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3367,14 +3335,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44901</v>
+        <v>45021</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3387,7 +3355,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3430,7 +3398,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3444,10 +3412,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45239</v>
+        <v>44900</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3460,7 +3428,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3503,7 +3471,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3517,10 +3485,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44944</v>
+        <v>44986</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3532,8 +3500,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3576,7 +3549,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3586,14 +3559,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44922</v>
+        <v>44929</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3606,7 +3579,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3666,7 +3639,7 @@
         <v>44929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3722,7 +3695,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3736,10 +3709,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45519</v>
+        <v>44960</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3752,7 +3725,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3795,7 +3768,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3805,14 +3778,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45203</v>
+        <v>45720</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3825,7 +3798,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3868,7 +3841,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3878,14 +3851,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45558</v>
+        <v>44929</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3898,7 +3871,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3941,7 +3914,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3951,14 +3924,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45063</v>
+        <v>44930</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3971,7 +3944,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4014,7 +3987,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4028,10 +4001,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44574</v>
+        <v>45642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4044,7 +4017,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4087,7 +4060,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4101,10 +4074,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45820</v>
+        <v>44805</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4117,7 +4090,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.8</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4160,7 +4133,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4174,10 +4147,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44922</v>
+        <v>45820</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4190,7 +4163,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>7.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4233,7 +4206,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4243,14 +4216,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44986</v>
+        <v>45898</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4260,11 +4233,6 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -4311,7 +4279,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4325,10 +4293,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45642</v>
+        <v>46058</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4341,7 +4309,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4384,7 +4352,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4394,14 +4362,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45898</v>
+        <v>44922</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4414,7 +4382,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4474,7 +4442,7 @@
         <v>45525</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4530,7 +4498,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4540,14 +4508,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44960</v>
+        <v>45394</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4560,7 +4528,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4603,7 +4571,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4613,14 +4581,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45034</v>
+        <v>45229</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4633,7 +4601,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4676,7 +4644,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4690,10 +4658,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44900</v>
+        <v>45338</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4706,7 +4674,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4749,7 +4717,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4763,10 +4731,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44715</v>
+        <v>45527</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4779,7 +4747,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4822,7 +4790,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4836,10 +4804,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45610</v>
+        <v>44901</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4852,7 +4820,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4895,7 +4863,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4909,10 +4877,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45177</v>
+        <v>44922</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4925,7 +4893,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4968,7 +4936,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4978,14 +4946,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44930</v>
+        <v>44502</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4997,8 +4965,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5041,7 +5014,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5055,10 +5028,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44929</v>
+        <v>45203</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5071,7 +5044,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5131,7 +5104,7 @@
         <v>45960</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5187,7 +5160,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5201,10 +5174,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45719</v>
+        <v>46112</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5217,7 +5190,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5260,7 +5233,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5274,10 +5247,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46112</v>
+        <v>44944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5290,7 +5263,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5350,7 +5323,7 @@
         <v>46125</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5406,7 +5379,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5420,10 +5393,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45249</v>
+        <v>45799</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5436,7 +5409,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5479,7 +5452,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5493,10 +5466,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45757</v>
+        <v>45754</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5509,7 +5482,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5552,7 +5525,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5566,10 +5539,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45754</v>
+        <v>45786</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5581,8 +5554,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5625,7 +5603,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5635,14 +5613,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45203</v>
+        <v>45642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5655,7 +5633,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5698,7 +5676,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5712,10 +5690,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45229</v>
+        <v>44979</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5728,7 +5706,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5771,7 +5749,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5785,10 +5763,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45229</v>
+        <v>45280</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5801,7 +5779,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5844,7 +5822,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5858,10 +5836,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46002</v>
+        <v>45401</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5874,7 +5852,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5917,7 +5895,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5931,10 +5909,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45580</v>
+        <v>45561</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5947,7 +5925,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5990,7 +5968,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6004,10 +5982,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45754</v>
+        <v>46002</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6020,7 +5998,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6080,7 +6058,7 @@
         <v>46000</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6136,7 +6114,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6150,10 +6128,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45799</v>
+        <v>44991</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6166,7 +6144,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6209,7 +6187,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6219,14 +6197,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45280</v>
+        <v>44984</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6239,7 +6217,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6282,7 +6260,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6296,10 +6274,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45527</v>
+        <v>45610</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6312,7 +6290,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6355,7 +6333,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6369,10 +6347,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45338</v>
+        <v>46146</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6385,7 +6363,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6428,7 +6406,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6442,10 +6420,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45786</v>
+        <v>45249</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6457,13 +6435,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6506,7 +6479,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6520,10 +6493,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44965</v>
+        <v>45754</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6536,7 +6509,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6579,7 +6552,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6593,10 +6566,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45642</v>
+        <v>45965</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6609,7 +6582,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6652,7 +6625,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6666,10 +6639,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45527</v>
+        <v>46195</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6682,7 +6655,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6725,7 +6698,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6739,10 +6712,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44502</v>
+        <v>45229</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6754,13 +6727,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6803,7 +6771,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6817,10 +6785,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46058</v>
+        <v>45166</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6833,7 +6801,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6876,7 +6844,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 20813-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6886,14 +6854,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45021</v>
+        <v>46141</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6906,7 +6874,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6949,7 +6917,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6963,10 +6931,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46146</v>
+        <v>45239</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6979,7 +6947,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7022,7 +6990,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7032,14 +7000,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45194</v>
+        <v>45932</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7052,7 +7020,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7095,7 +7063,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7105,14 +7073,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45619</v>
+        <v>45527</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7125,7 +7093,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7168,7 +7136,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7182,10 +7150,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45965</v>
+        <v>46273</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7198,7 +7166,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7241,7 +7209,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7255,10 +7223,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45775</v>
+        <v>45324</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7271,7 +7239,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7314,7 +7282,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7328,10 +7296,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45561</v>
+        <v>44965</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7344,7 +7312,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7387,7 +7355,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7401,10 +7369,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46195</v>
+        <v>45558</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7417,7 +7385,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7460,7 +7428,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7474,10 +7442,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45166</v>
+        <v>45063</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7490,7 +7458,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7533,7 +7501,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7547,10 +7515,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44805</v>
+        <v>45194</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7563,7 +7531,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7606,7 +7574,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7616,14 +7584,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44953</v>
+        <v>45519</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7636,7 +7604,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7679,7 +7647,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7689,14 +7657,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44953</v>
+        <v>45775</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7709,7 +7677,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7752,7 +7720,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7766,10 +7734,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45191</v>
+        <v>44845</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7782,7 +7750,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7825,7 +7793,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7835,14 +7803,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44755</v>
+        <v>45034</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7855,7 +7823,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7898,7 +7866,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7912,10 +7880,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45591</v>
+        <v>44515</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7928,7 +7896,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7971,7 +7939,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7985,10 +7953,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44602</v>
+        <v>44922</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8001,7 +7969,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8044,7 +8012,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8058,10 +8026,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45107</v>
+        <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8074,7 +8042,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8117,7 +8085,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8131,10 +8099,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44922</v>
+        <v>45253</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8147,7 +8115,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8190,7 +8158,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8200,14 +8168,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45049</v>
+        <v>45580</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8220,7 +8188,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8263,7 +8231,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20813-2026</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8277,10 +8245,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46141</v>
+        <v>45757</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8293,7 +8261,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8336,7 +8304,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8346,14 +8314,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44922</v>
+        <v>45049</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8366,7 +8334,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8409,7 +8377,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8423,10 +8391,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44929</v>
+        <v>45203</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8439,7 +8407,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8482,7 +8450,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8496,10 +8464,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44991</v>
+        <v>44602</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8512,7 +8480,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8555,7 +8523,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8565,14 +8533,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45932</v>
+        <v>45251</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8585,7 +8553,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8628,7 +8596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8638,14 +8606,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45394</v>
+        <v>44755</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8658,7 +8626,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8701,7 +8669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8715,10 +8683,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45324</v>
+        <v>45591</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8731,7 +8699,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8774,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8788,10 +8756,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44984</v>
+        <v>45619</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8804,7 +8772,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8847,7 +8815,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8861,10 +8829,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44845</v>
+        <v>45719</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8877,7 +8845,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8920,7 +8888,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8930,14 +8898,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46273</v>
+        <v>44953</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8950,7 +8918,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8993,7 +8961,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9003,14 +8971,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45251</v>
+        <v>44953</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9023,7 +8991,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9066,7 +9034,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9080,10 +9048,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45253</v>
+        <v>45229</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9096,7 +9064,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9139,7 +9107,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9153,10 +9121,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44979</v>
+        <v>45177</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9169,7 +9137,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9212,7 +9180,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9226,10 +9194,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45617</v>
+        <v>45680</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9242,7 +9210,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9285,7 +9253,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9299,10 +9267,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45680</v>
+        <v>45617</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9315,7 +9283,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9358,7 +9326,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9372,10 +9340,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45789</v>
+        <v>45666</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9388,7 +9356,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9431,7 +9399,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9445,10 +9413,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45709</v>
+        <v>45789</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9461,7 +9429,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9504,7 +9472,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9518,10 +9486,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45666</v>
+        <v>45579</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9534,7 +9502,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9577,7 +9545,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9591,10 +9559,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45579</v>
+        <v>45709</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9607,7 +9575,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9650,24 +9618,24 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45720</v>
+        <v>45222</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9680,7 +9648,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9720,7 +9688,7 @@
       </c>
       <c r="V120" s="2" t="inlineStr"/>
     </row>
-    <row r="121" ht="15" customHeight="1">
+    <row r="121">
       <c r="A121" t="inlineStr">
         <is>
           <t>S 3071-2022</t>
@@ -9740,7 +9708,7 @@
         <v>44715</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9792,79 +9760,6 @@
         <v>0</v>
       </c>
       <c r="V121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>S 3719-2023</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E122" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I122" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 417-2023</t>
+          <t>A 2764-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44929</v>
+        <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,153 +871,153 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Ask
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 417-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Nattskärra
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 2764-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 25330-2026</t>
+          <t>A 29724-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46176</v>
+        <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>11.8</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1080,10 +1080,10 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1092,148 +1092,148 @@
         </is>
       </c>
       <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29724-2022 artfynd.xlsx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29724-2022 karta.png", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29724-2022 georefererad karta.tif", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 29724-2022 karta knärot.png", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29724-2022 FSC-klagomål.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29724-2022 FSC-klagomål mail.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29724-2022 tillsynsbegäran.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29724-2022 tillsynsbegäran mail.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 25330-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 25330-2026 artfynd.xlsx", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 25330-2026 karta.png", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 25330-2026 georefererad karta.tif", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 25330-2026 karta knärot.png", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 25330-2026 FSC-klagomål.docx", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 25330-2026 FSC-klagomål mail.docx", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 25330-2026 tillsynsbegäran.docx", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 25330-2026 tillsynsbegäran mail.docx", "A 25330-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 29724-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44755</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>7</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Flagellkvastmossa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29724-2022 artfynd.xlsx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29724-2022 karta.png", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29724-2022 georefererad karta.tif", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 29724-2022 karta knärot.png", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29724-2022 FSC-klagomål.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29724-2022 FSC-klagomål mail.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29724-2022 tillsynsbegäran.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29724-2022 tillsynsbegäran mail.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44690</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 29819-2025</t>
+          <t>A 56101-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45825</v>
+        <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1409,50 +1409,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 56101-2025</t>
+          <t>A 2763-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1466,10 +1462,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45973</v>
+        <v>44944</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1482,13 +1478,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1522,35 +1518,35 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
     </row>
@@ -1574,7 +1570,7 @@
         <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1658,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2763-2023</t>
+          <t>A 29819-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1676,10 +1672,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44944</v>
+        <v>45825</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1692,7 +1688,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1728,39 +1724,43 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
         <v/>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
         <v>44602</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44734</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>44715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>44804</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 495-2022</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44566</v>
+        <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,13 +2755,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2804,7 +2799,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 496-2022</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2818,10 +2813,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44566</v>
+        <v>45401</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,13 +2828,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2882,7 +2872,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 65095-2021</t>
+          <t>A 495-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2896,10 +2886,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44515</v>
+        <v>44566</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2911,8 +2901,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2955,7 +2950,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61986-2021</t>
+          <t>A 496-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2969,10 +2964,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44502</v>
+        <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2986,11 +2981,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3033,7 +3028,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 61986-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3047,10 +3042,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44922</v>
+        <v>44502</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3062,8 +3057,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 65095-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44715</v>
+        <v>44515</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45107</v>
+        <v>45229</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45191</v>
+        <v>44901</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3335,14 +3335,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45021</v>
+        <v>45239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44900</v>
+        <v>44944</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44986</v>
+        <v>45642</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3500,13 +3500,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3549,7 +3544,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3559,14 +3554,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44929</v>
+        <v>44922</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3579,7 +3574,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3622,7 +3617,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3636,10 +3631,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44929</v>
+        <v>45898</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3695,7 +3690,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3705,14 +3700,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44960</v>
+        <v>44929</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3725,7 +3720,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3768,7 +3763,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3778,14 +3773,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45720</v>
+        <v>45203</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3798,7 +3793,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3841,7 +3836,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3851,14 +3846,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44929</v>
+        <v>45519</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3871,7 +3866,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3914,7 +3909,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3924,14 +3919,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44930</v>
+        <v>45063</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3944,7 +3939,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3987,7 +3982,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4001,10 +3996,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45642</v>
+        <v>44574</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4017,7 +4012,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4060,7 +4055,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4074,10 +4069,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44805</v>
+        <v>45558</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4090,7 +4085,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4133,7 +4128,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4147,10 +4142,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45820</v>
+        <v>46112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4163,7 +4158,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4206,7 +4201,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4216,14 +4211,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45898</v>
+        <v>46125</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4236,7 +4231,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4279,7 +4274,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4293,10 +4288,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46058</v>
+        <v>45166</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4309,7 +4304,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4352,7 +4347,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4369,7 +4364,7 @@
         <v>44922</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4382,7 +4377,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4425,7 +4420,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4439,10 +4434,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45525</v>
+        <v>45754</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4455,7 +4450,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4498,7 +4493,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4508,14 +4503,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45394</v>
+        <v>44986</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4527,8 +4522,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45229</v>
+        <v>46000</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45338</v>
+        <v>45799</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45527</v>
+        <v>45280</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4790,7 +4790,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44901</v>
+        <v>45960</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44922</v>
+        <v>45786</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4892,8 +4892,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4936,7 +4941,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4950,10 +4955,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44502</v>
+        <v>45642</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4965,13 +4970,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5014,7 +5014,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5024,14 +5024,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45203</v>
+        <v>44960</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45960</v>
+        <v>45034</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5160,7 +5160,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46112</v>
+        <v>44805</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5233,7 +5233,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44944</v>
+        <v>44953</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5316,14 +5316,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46125</v>
+        <v>44953</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5379,7 +5379,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45799</v>
+        <v>44900</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5452,7 +5452,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5466,10 +5466,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45754</v>
+        <v>44715</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5539,10 +5539,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45786</v>
+        <v>45610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5554,13 +5554,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5603,7 +5598,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5617,10 +5612,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45642</v>
+        <v>45191</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5633,7 +5628,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5676,7 +5671,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5690,10 +5685,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44979</v>
+        <v>44755</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5706,7 +5701,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5749,7 +5744,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5763,10 +5758,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45280</v>
+        <v>45177</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5779,7 +5774,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5822,7 +5817,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5836,10 +5831,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45401</v>
+        <v>45591</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5852,7 +5847,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5895,7 +5890,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5909,10 +5904,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45561</v>
+        <v>46146</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5925,7 +5920,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5968,7 +5963,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5982,10 +5977,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46002</v>
+        <v>44602</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5998,7 +5993,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6041,7 +6036,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6055,10 +6050,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46000</v>
+        <v>45107</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6071,7 +6066,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6114,7 +6109,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6124,14 +6119,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44991</v>
+        <v>44930</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6144,7 +6139,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6187,7 +6182,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6201,10 +6196,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44984</v>
+        <v>44929</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6217,7 +6212,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6260,7 +6255,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6274,10 +6269,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45610</v>
+        <v>46002</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6290,7 +6285,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6333,7 +6328,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6347,10 +6342,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46146</v>
+        <v>45719</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6363,7 +6358,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6406,7 +6401,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6420,10 +6415,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45249</v>
+        <v>45965</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6436,7 +6431,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6479,7 +6474,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6493,10 +6488,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45754</v>
+        <v>45249</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6509,7 +6504,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6552,7 +6547,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6566,10 +6561,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45965</v>
+        <v>44922</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6582,7 +6577,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6625,7 +6620,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6639,10 +6634,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46195</v>
+        <v>45757</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6655,7 +6650,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6698,7 +6693,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6712,10 +6707,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45229</v>
+        <v>45754</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6728,7 +6723,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6771,7 +6766,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6781,14 +6776,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45166</v>
+        <v>45203</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6801,7 +6796,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6844,7 +6839,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 20813-2026</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6858,10 +6853,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46141</v>
+        <v>45229</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6874,7 +6869,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6917,7 +6912,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6931,10 +6926,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45239</v>
+        <v>45229</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6947,7 +6942,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6990,7 +6985,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7000,14 +6995,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45932</v>
+        <v>45580</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7020,7 +7015,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7063,7 +7058,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7073,14 +7068,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45527</v>
+        <v>45049</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7093,7 +7088,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7136,7 +7131,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7150,10 +7145,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46273</v>
+        <v>46058</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7166,7 +7161,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7209,7 +7204,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7223,10 +7218,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45324</v>
+        <v>45527</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7239,7 +7234,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7282,7 +7277,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7296,10 +7291,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44965</v>
+        <v>45338</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7312,7 +7307,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7355,7 +7350,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7369,10 +7364,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45558</v>
+        <v>44965</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7385,7 +7380,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7428,7 +7423,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7442,10 +7437,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45063</v>
+        <v>45527</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7458,7 +7453,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7501,7 +7496,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7515,10 +7510,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45194</v>
+        <v>44502</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7530,8 +7525,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7574,7 +7574,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45519</v>
+        <v>46195</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7647,7 +7647,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45775</v>
+        <v>44922</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7720,7 +7720,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7730,14 +7730,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44845</v>
+        <v>44929</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7803,14 +7803,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45034</v>
+        <v>44991</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7876,14 +7876,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44515</v>
+        <v>45021</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7939,7 +7939,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7949,14 +7949,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44922</v>
+        <v>45394</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8012,7 +8012,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44574</v>
+        <v>45324</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8095,14 +8095,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45253</v>
+        <v>44984</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8158,7 +8158,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 20813-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8172,10 +8172,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45580</v>
+        <v>46141</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8231,7 +8231,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45757</v>
+        <v>45194</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8304,7 +8304,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45049</v>
+        <v>45619</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8377,7 +8377,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8391,10 +8391,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45203</v>
+        <v>45932</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44602</v>
+        <v>44845</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8523,7 +8523,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8537,10 +8537,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45251</v>
+        <v>45775</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44755</v>
+        <v>45561</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,7 +8669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45591</v>
+        <v>45251</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8752,14 +8752,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45619</v>
+        <v>46273</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8815,7 +8815,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8829,10 +8829,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45719</v>
+        <v>45253</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8888,7 +8888,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8898,14 +8898,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44953</v>
+        <v>44979</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8961,7 +8961,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8971,14 +8971,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44953</v>
+        <v>45617</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9034,7 +9034,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45229</v>
+        <v>45680</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9107,7 +9107,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45177</v>
+        <v>45789</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9180,7 +9180,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45680</v>
+        <v>45709</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9253,7 +9253,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45617</v>
+        <v>45666</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9326,7 +9326,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9340,10 +9340,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45666</v>
+        <v>45579</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9399,7 +9399,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45789</v>
+        <v>45720</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9472,7 +9472,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45579</v>
+        <v>45820</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9545,7 +9545,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45709</v>
+        <v>45525</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9632,10 +9632,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9691,7 +9691,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE121"/>
+  <dimension ref="A1:AE125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 2764-2023</t>
+          <t>A 417-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44944</v>
+        <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2764-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Ask
 Vårstarr</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 417-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>46176</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44690</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 56101-2025</t>
+          <t>A 29819-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45973</v>
+        <v>45825</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1409,361 +1409,361 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 56101-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Hasselticka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 2763-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>44944</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>2.5</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 31382-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>46219</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>1.6</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 29819-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45825</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>44602</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44734</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10328-2022</t>
+          <t>A 6822-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44623</v>
+        <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6822-2022</t>
+          <t>A 10328-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44602</v>
+        <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23080-2022</t>
+          <t>A 65112-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44715</v>
+        <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 65112-2021</t>
+          <t>A 23080-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44515</v>
+        <v>44715</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>44804</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 495-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44515</v>
+        <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,8 +2755,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2799,7 +2804,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 496-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,10 +2818,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45401</v>
+        <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2828,8 +2833,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2872,7 +2882,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 495-2022</t>
+          <t>A 65095-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,10 +2896,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44566</v>
+        <v>44515</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2901,13 +2911,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2950,7 +2955,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 496-2022</t>
+          <t>A 61986-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2964,10 +2969,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44566</v>
+        <v>44502</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2981,11 +2986,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3028,7 +3033,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 61986-2021</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3042,10 +3047,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44502</v>
+        <v>44922</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3057,13 +3062,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 65095-2021</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44515</v>
+        <v>44715</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45229</v>
+        <v>45107</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44901</v>
+        <v>45191</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45239</v>
+        <v>44900</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3408,14 +3408,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44944</v>
+        <v>45021</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45642</v>
+        <v>44986</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3500,8 +3500,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3544,7 +3549,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3554,14 +3559,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44922</v>
+        <v>44929</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3574,7 +3579,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3617,7 +3622,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3631,10 +3636,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45898</v>
+        <v>44929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3690,7 +3695,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3700,14 +3705,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44929</v>
+        <v>44960</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3720,7 +3725,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3763,7 +3768,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3777,10 +3782,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45203</v>
+        <v>44929</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3793,7 +3798,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3836,7 +3841,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3846,14 +3851,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45519</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3866,7 +3871,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3909,7 +3914,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3923,10 +3928,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45063</v>
+        <v>44805</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3939,7 +3944,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3982,7 +3987,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3996,10 +4001,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44574</v>
+        <v>45642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4012,7 +4017,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4055,7 +4060,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4069,10 +4074,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45558</v>
+        <v>45820</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4085,7 +4090,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4128,7 +4133,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4138,14 +4143,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46112</v>
+        <v>45898</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4158,7 +4163,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4201,7 +4206,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4215,10 +4220,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46125</v>
+        <v>44922</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4231,7 +4236,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4274,7 +4279,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4284,14 +4289,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45166</v>
+        <v>45394</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4304,7 +4309,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4347,7 +4352,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4361,10 +4366,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44922</v>
+        <v>45229</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4377,7 +4382,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4420,7 +4425,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4434,10 +4439,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45754</v>
+        <v>45338</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4493,7 +4498,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4507,10 +4512,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44986</v>
+        <v>45527</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4522,13 +4527,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46000</v>
+        <v>45525</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45799</v>
+        <v>44901</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45280</v>
+        <v>44922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4790,7 +4790,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45960</v>
+        <v>44502</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4819,8 +4819,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4863,7 +4868,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4873,14 +4878,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45786</v>
+        <v>45203</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4892,13 +4897,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4941,7 +4941,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45642</v>
+        <v>44944</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5014,7 +5014,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44960</v>
+        <v>46058</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45034</v>
+        <v>45960</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5160,7 +5160,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44805</v>
+        <v>44979</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5233,7 +5233,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44953</v>
+        <v>45401</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5306,7 +5306,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5316,14 +5316,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44953</v>
+        <v>45561</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5379,7 +5379,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44900</v>
+        <v>46002</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5452,7 +5452,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5466,10 +5466,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44715</v>
+        <v>44991</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5535,14 +5535,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45610</v>
+        <v>44984</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45191</v>
+        <v>45610</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5671,7 +5671,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5685,10 +5685,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44755</v>
+        <v>45249</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5744,7 +5744,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45177</v>
+        <v>45754</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45591</v>
+        <v>46112</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5963,7 +5963,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44602</v>
+        <v>45229</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6036,7 +6036,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45107</v>
+        <v>45166</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6109,7 +6109,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6119,14 +6119,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44930</v>
+        <v>45799</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6192,14 +6192,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44929</v>
+        <v>45754</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46002</v>
+        <v>45786</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6284,8 +6284,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6328,7 +6333,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6342,10 +6347,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45719</v>
+        <v>45239</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6358,7 +6363,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6401,7 +6406,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6415,10 +6420,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45965</v>
+        <v>45642</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6431,7 +6436,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6474,7 +6479,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6488,10 +6493,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45249</v>
+        <v>45280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6504,7 +6509,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6547,7 +6552,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6561,10 +6566,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44922</v>
+        <v>45527</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6577,7 +6582,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6620,7 +6625,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6634,10 +6639,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45757</v>
+        <v>46000</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6650,7 +6655,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6693,7 +6698,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6707,10 +6712,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45754</v>
+        <v>45324</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6723,7 +6728,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6766,7 +6771,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6776,14 +6781,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45203</v>
+        <v>46146</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6796,7 +6801,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6839,7 +6844,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6853,10 +6858,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45229</v>
+        <v>44965</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6869,7 +6874,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6912,7 +6917,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6926,10 +6931,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45229</v>
+        <v>45558</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6942,7 +6947,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6985,7 +6990,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6999,10 +7004,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45580</v>
+        <v>45063</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7015,7 +7020,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7058,7 +7063,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7068,14 +7073,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45049</v>
+        <v>45194</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7088,7 +7093,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7131,7 +7136,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7145,10 +7150,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46058</v>
+        <v>45519</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7161,7 +7166,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7204,7 +7209,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7218,10 +7223,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45527</v>
+        <v>45775</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7234,7 +7239,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7277,7 +7282,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7291,10 +7296,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45338</v>
+        <v>44845</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7350,7 +7355,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7364,10 +7369,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44965</v>
+        <v>45965</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7380,7 +7385,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7423,7 +7428,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7433,14 +7438,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45527</v>
+        <v>45034</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7453,7 +7458,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7496,7 +7501,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7510,10 +7515,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44502</v>
+        <v>44515</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7525,13 +7530,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7574,7 +7574,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46195</v>
+        <v>44922</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7647,7 +7647,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44922</v>
+        <v>44574</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7720,7 +7720,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7730,14 +7730,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44929</v>
+        <v>45253</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44991</v>
+        <v>45580</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7876,14 +7876,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45021</v>
+        <v>45757</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7939,7 +7939,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7949,14 +7949,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45394</v>
+        <v>46195</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8012,7 +8012,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8022,14 +8022,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45324</v>
+        <v>45049</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 20813-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8095,14 +8095,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44984</v>
+        <v>46141</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8158,7 +8158,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20813-2026</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8168,14 +8168,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46141</v>
+        <v>45203</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.2</v>
+        <v>0.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8231,7 +8231,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45194</v>
+        <v>44602</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8304,7 +8304,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45619</v>
+        <v>45251</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8394,7 +8394,7 @@
         <v>45932</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44845</v>
+        <v>44755</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8523,7 +8523,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8537,10 +8537,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45775</v>
+        <v>45591</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8606,14 +8606,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45561</v>
+        <v>45619</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,7 +8669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45251</v>
+        <v>45719</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8752,14 +8752,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46273</v>
+        <v>44953</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8815,7 +8815,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8825,14 +8825,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45253</v>
+        <v>44953</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8888,7 +8888,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44979</v>
+        <v>46273</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8961,7 +8961,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45617</v>
+        <v>45229</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9034,7 +9034,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45680</v>
+        <v>45177</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9107,7 +9107,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45789</v>
+        <v>46281</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9180,7 +9180,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45709</v>
+        <v>46281</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9253,7 +9253,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45666</v>
+        <v>46281</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9326,7 +9326,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9340,10 +9340,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45579</v>
+        <v>46281</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9399,7 +9399,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45720</v>
+        <v>45680</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9472,7 +9472,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45820</v>
+        <v>45617</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>7.8</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9545,7 +9545,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45525</v>
+        <v>45666</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9618,148 +9618,440 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
+          <t>A 22828-2025</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>45789</v>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>A 45599-2024</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>45579</v>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>A 8450-2025</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>45709</v>
+      </c>
+      <c r="E122" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>A 10462-2025</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>45720</v>
+      </c>
+      <c r="E123" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124" ht="15" customHeight="1">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>S 3719-2023</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E124" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>S 3071-2022</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D120" s="1" t="n">
+      <c r="D125" s="1" t="n">
         <v>44715</v>
       </c>
-      <c r="E120" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I120" t="n">
+      <c r="E125" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
         <v>0.7</v>
       </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0</v>
-      </c>
-      <c r="V120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>S 3719-2023</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E121" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I121" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="2" t="inlineStr"/>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE125"/>
+  <dimension ref="A1:AE126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 417-2023</t>
+          <t>A 2764-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44929</v>
+        <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,153 +871,153 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Ask
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 417-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Nattskärra
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 2764-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 29724-2022</t>
+          <t>A 25330-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44755</v>
+        <v>46176</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>11.8</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1080,10 +1080,10 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1092,148 +1092,148 @@
         </is>
       </c>
       <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 25330-2026 artfynd.xlsx", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 25330-2026 karta.png", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 25330-2026 georefererad karta.tif", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 25330-2026 karta knärot.png", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 25330-2026 FSC-klagomål.docx", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 25330-2026 FSC-klagomål mail.docx", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 25330-2026 tillsynsbegäran.docx", "A 25330-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 25330-2026 tillsynsbegäran mail.docx", "A 25330-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 29724-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44755</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29724-2022 artfynd.xlsx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29724-2022 karta.png", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29724-2022 georefererad karta.tif", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 29724-2022 karta knärot.png", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29724-2022 FSC-klagomål.docx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29724-2022 FSC-klagomål mail.docx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29724-2022 tillsynsbegäran.docx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29724-2022 tillsynsbegäran mail.docx", "A 29724-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 25330-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46176</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Flagellkvastmossa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 25330-2026 artfynd.xlsx", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 25330-2026 karta.png", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 25330-2026 georefererad karta.tif", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 25330-2026 karta knärot.png", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 25330-2026 FSC-klagomål.docx", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 25330-2026 FSC-klagomål mail.docx", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 25330-2026 tillsynsbegäran.docx", "A 25330-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 25330-2026 tillsynsbegäran mail.docx", "A 25330-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44690</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45825</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45973</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2763-2023</t>
+          <t>A 31382-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44944</v>
+        <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1627,143 +1627,143 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 2763-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 31382-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>44602</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44734</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>44623</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 65112-2021</t>
+          <t>A 23080-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44515</v>
+        <v>44715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23080-2022</t>
+          <t>A 65112-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44715</v>
+        <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>44804</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44515</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44502</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44922</v>
+        <v>45229</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44715</v>
+        <v>44515</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45107</v>
+        <v>45401</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45191</v>
+        <v>44901</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44900</v>
+        <v>45239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3408,14 +3408,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45021</v>
+        <v>44944</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44986</v>
+        <v>44922</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3500,13 +3500,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3549,7 +3544,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3566,7 +3561,7 @@
         <v>44929</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3579,7 +3574,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3622,7 +3617,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3632,14 +3627,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44929</v>
+        <v>45519</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3652,7 +3647,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3695,7 +3690,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3705,14 +3700,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44960</v>
+        <v>45203</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3725,7 +3720,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3768,7 +3763,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3778,14 +3773,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44929</v>
+        <v>45558</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3798,7 +3793,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3841,7 +3836,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3851,14 +3846,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44930</v>
+        <v>44574</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3871,7 +3866,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3914,7 +3909,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3928,10 +3923,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44805</v>
+        <v>45063</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3944,7 +3939,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3987,7 +3982,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4001,10 +3996,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45642</v>
+        <v>45820</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4017,7 +4012,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4060,7 +4055,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4074,10 +4069,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45820</v>
+        <v>44922</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4090,7 +4085,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.8</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4133,7 +4128,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4143,14 +4138,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45898</v>
+        <v>44986</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4160,6 +4155,11 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -4206,7 +4206,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44922</v>
+        <v>45525</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4279,7 +4279,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4289,14 +4289,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45394</v>
+        <v>44960</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4352,7 +4352,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4362,14 +4362,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45229</v>
+        <v>45034</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4425,7 +4425,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45338</v>
+        <v>46112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4498,7 +4498,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45527</v>
+        <v>45642</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45525</v>
+        <v>46125</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44901</v>
+        <v>44900</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44922</v>
+        <v>44715</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4790,7 +4790,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44502</v>
+        <v>45610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4819,13 +4819,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4868,7 +4863,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4882,10 +4877,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45203</v>
+        <v>45898</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4898,7 +4893,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4941,7 +4936,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4955,10 +4950,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44944</v>
+        <v>45177</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4971,7 +4966,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5014,7 +5009,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5028,10 +5023,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46058</v>
+        <v>45754</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5044,7 +5039,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5087,7 +5082,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5101,10 +5096,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45960</v>
+        <v>46000</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5117,7 +5112,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5160,7 +5155,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5174,10 +5169,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44979</v>
+        <v>45799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5190,7 +5185,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5233,7 +5228,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5243,14 +5238,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45401</v>
+        <v>44930</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5263,7 +5258,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5306,7 +5301,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5316,14 +5311,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45561</v>
+        <v>44929</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5336,7 +5331,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5379,7 +5374,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5393,10 +5388,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46002</v>
+        <v>45280</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5409,7 +5404,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5452,7 +5447,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5466,10 +5461,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44991</v>
+        <v>45719</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5482,7 +5477,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5525,7 +5520,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5535,14 +5530,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44984</v>
+        <v>45786</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5554,8 +5549,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45610</v>
+        <v>45642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         <v>45249</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45754</v>
+        <v>45757</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46112</v>
+        <v>45754</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5900,14 +5900,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46125</v>
+        <v>45203</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5963,7 +5963,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5980,7 +5980,7 @@
         <v>45229</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6036,7 +6036,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45166</v>
+        <v>46146</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6109,7 +6109,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6123,10 +6123,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45799</v>
+        <v>45229</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45754</v>
+        <v>45580</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45786</v>
+        <v>45527</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6284,13 +6284,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6333,7 +6328,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6347,10 +6342,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45239</v>
+        <v>45965</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6363,7 +6358,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6406,7 +6401,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6420,10 +6415,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45642</v>
+        <v>45338</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6436,7 +6431,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6479,7 +6474,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6493,10 +6488,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45280</v>
+        <v>44965</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6509,7 +6504,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6552,7 +6547,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6569,7 +6564,7 @@
         <v>45527</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6582,7 +6577,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6625,7 +6620,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6639,10 +6634,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46000</v>
+        <v>44502</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6654,8 +6649,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6698,7 +6698,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6708,14 +6708,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45324</v>
+        <v>45021</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46146</v>
+        <v>45960</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6844,7 +6844,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44965</v>
+        <v>46195</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6917,7 +6917,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45558</v>
+        <v>45194</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6990,7 +6990,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7000,14 +7000,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45063</v>
+        <v>45619</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7063,7 +7063,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7077,10 +7077,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45194</v>
+        <v>45775</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7136,7 +7136,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45519</v>
+        <v>45561</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7209,7 +7209,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 20813-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7223,10 +7223,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45775</v>
+        <v>46141</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7282,7 +7282,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7292,14 +7292,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44845</v>
+        <v>45932</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7355,7 +7355,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45965</v>
+        <v>46002</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7428,7 +7428,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7438,14 +7438,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45034</v>
+        <v>46273</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7501,7 +7501,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44515</v>
+        <v>45166</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7574,7 +7574,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44922</v>
+        <v>44805</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7647,7 +7647,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7657,14 +7657,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44574</v>
+        <v>44953</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7720,7 +7720,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7730,14 +7730,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45253</v>
+        <v>44953</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45580</v>
+        <v>46281</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7880,10 +7880,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45757</v>
+        <v>46281</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7939,7 +7939,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7953,10 +7953,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46195</v>
+        <v>45191</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8012,7 +8012,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8022,14 +8022,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45049</v>
+        <v>44755</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20813-2026</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46141</v>
+        <v>45591</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8158,7 +8158,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8168,14 +8168,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45203</v>
+        <v>46282</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8231,7 +8231,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44602</v>
+        <v>46281</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8304,7 +8304,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45251</v>
+        <v>44602</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8377,7 +8377,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8387,14 +8387,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45932</v>
+        <v>45107</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44755</v>
+        <v>46281</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8523,7 +8523,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8537,10 +8537,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45591</v>
+        <v>44922</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45619</v>
+        <v>45049</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,7 +8669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45719</v>
+        <v>44922</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44953</v>
+        <v>44929</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8815,7 +8815,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8825,14 +8825,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44953</v>
+        <v>44991</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46273</v>
+        <v>46058</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8961,7 +8961,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8971,14 +8971,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45229</v>
+        <v>45394</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9034,7 +9034,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45177</v>
+        <v>45324</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9107,7 +9107,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9117,14 +9117,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46281</v>
+        <v>44984</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9180,7 +9180,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46281</v>
+        <v>44845</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9253,7 +9253,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46281</v>
+        <v>45251</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9326,7 +9326,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9340,10 +9340,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46281</v>
+        <v>45253</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9399,7 +9399,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45680</v>
+        <v>44979</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9489,7 +9489,7 @@
         <v>45617</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45666</v>
+        <v>45680</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9635,7 +9635,7 @@
         <v>45789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45579</v>
+        <v>45709</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9764,7 +9764,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45709</v>
+        <v>45666</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9837,7 +9837,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45720</v>
+        <v>45579</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9910,24 +9910,24 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45222</v>
+        <v>45720</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="V124" s="2" t="inlineStr"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
           <t>S 3071-2022</t>
@@ -10000,7 +10000,7 @@
         <v>44715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10052,6 +10052,79 @@
         <v>0</v>
       </c>
       <c r="V125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>S 3719-2023</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E126" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 2764-2023</t>
+          <t>A 417-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44944</v>
+        <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,153 +871,153 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2764-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Ask
 Vårstarr</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 417-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 25330-2026</t>
+          <t>A 29724-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46176</v>
+        <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>11.8</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1080,10 +1080,10 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1092,148 +1092,148 @@
         </is>
       </c>
       <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29724-2022 artfynd.xlsx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29724-2022 karta.png", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29724-2022 georefererad karta.tif", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 29724-2022 karta knärot.png", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29724-2022 FSC-klagomål.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29724-2022 FSC-klagomål mail.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29724-2022 tillsynsbegäran.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29724-2022 tillsynsbegäran mail.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 25330-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 25330-2026 artfynd.xlsx", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 25330-2026 karta.png", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 25330-2026 georefererad karta.tif", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 25330-2026 karta knärot.png", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 25330-2026 FSC-klagomål.docx", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 25330-2026 FSC-klagomål mail.docx", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 25330-2026 tillsynsbegäran.docx", "A 25330-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 25330-2026 tillsynsbegäran mail.docx", "A 25330-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 29724-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44755</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>7</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Flagellkvastmossa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29724-2022 artfynd.xlsx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29724-2022 karta.png", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29724-2022 georefererad karta.tif", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 29724-2022 karta knärot.png", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29724-2022 FSC-klagomål.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29724-2022 FSC-klagomål mail.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29724-2022 tillsynsbegäran.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29724-2022 tillsynsbegäran mail.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44690</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 29819-2025</t>
+          <t>A 56101-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45825</v>
+        <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1409,50 +1409,46 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 56101-2025</t>
+          <t>A 2763-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1466,10 +1462,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45973</v>
+        <v>44944</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1482,13 +1478,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1522,35 +1518,35 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
     </row>
@@ -1574,7 +1570,7 @@
         <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1662,7 +1658,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2763-2023</t>
+          <t>A 29819-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1676,10 +1672,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44944</v>
+        <v>45825</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1692,7 +1688,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1728,39 +1724,43 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
         <v/>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
         <v>44602</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44734</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6822-2022</t>
+          <t>A 10328-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44602</v>
+        <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10328-2022</t>
+          <t>A 6822-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44623</v>
+        <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>44715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>44804</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44515</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44502</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45229</v>
+        <v>44922</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44515</v>
+        <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45401</v>
+        <v>45191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3262,14 +3262,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44901</v>
+        <v>45021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45239</v>
+        <v>44900</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44944</v>
+        <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3427,8 +3427,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3471,7 +3476,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3485,10 +3490,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44922</v>
+        <v>44715</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3501,7 +3506,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3544,7 +3549,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3554,14 +3559,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44929</v>
+        <v>44960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3574,7 +3579,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3617,7 +3622,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3627,14 +3632,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45519</v>
+        <v>44929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3647,7 +3652,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3690,7 +3695,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45203</v>
+        <v>44929</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3720,7 +3725,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3763,7 +3768,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3773,14 +3778,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45558</v>
+        <v>44929</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3793,7 +3798,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3836,7 +3841,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3846,14 +3851,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44574</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3866,7 +3871,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3909,7 +3914,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3923,10 +3928,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45063</v>
+        <v>44805</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3939,7 +3944,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3982,7 +3987,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3996,10 +4001,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45820</v>
+        <v>44922</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4012,7 +4017,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.8</v>
+        <v>3.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4055,7 +4060,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4065,14 +4070,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44922</v>
+        <v>45394</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4085,7 +4090,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4128,7 +4133,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4142,10 +4147,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44986</v>
+        <v>45229</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4157,13 +4162,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4206,7 +4206,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45525</v>
+        <v>45338</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4279,7 +4279,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44960</v>
+        <v>45527</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4352,7 +4352,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4362,14 +4362,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45034</v>
+        <v>44901</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4425,7 +4425,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46112</v>
+        <v>44922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4498,7 +4498,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45642</v>
+        <v>44502</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4527,8 +4527,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4571,7 +4576,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4581,14 +4586,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46125</v>
+        <v>45203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4644,7 +4649,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4658,10 +4663,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44900</v>
+        <v>44944</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4674,7 +4679,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4717,7 +4722,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4731,10 +4736,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44715</v>
+        <v>45642</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4747,7 +4752,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4790,7 +4795,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4804,10 +4809,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45610</v>
+        <v>44979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4820,7 +4825,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4863,7 +4868,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4873,14 +4878,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45898</v>
+        <v>45280</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4893,7 +4898,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4936,7 +4941,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4950,10 +4955,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45177</v>
+        <v>45401</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4966,7 +4971,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5009,7 +5014,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5023,10 +5028,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45754</v>
+        <v>45642</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5039,7 +5044,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5082,7 +5087,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5096,10 +5101,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46000</v>
+        <v>45561</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5112,7 +5117,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5155,7 +5160,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5165,14 +5170,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45799</v>
+        <v>45898</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5185,7 +5190,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5228,7 +5233,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5238,14 +5243,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44930</v>
+        <v>46000</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5258,7 +5263,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5301,7 +5306,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5311,14 +5316,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44929</v>
+        <v>44991</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5331,7 +5336,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5374,7 +5379,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5384,14 +5389,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45280</v>
+        <v>44984</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5404,7 +5409,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5447,7 +5452,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5461,10 +5466,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45719</v>
+        <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5477,7 +5482,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5520,7 +5525,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5534,10 +5539,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45786</v>
+        <v>45249</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5549,13 +5554,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45642</v>
+        <v>46146</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5671,7 +5671,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5685,10 +5685,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45249</v>
+        <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5744,7 +5744,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45757</v>
+        <v>45229</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45754</v>
+        <v>45166</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5900,14 +5900,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45203</v>
+        <v>45960</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5963,7 +5963,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45229</v>
+        <v>45239</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6036,7 +6036,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46146</v>
+        <v>45527</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6109,7 +6109,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6123,10 +6123,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45229</v>
+        <v>45324</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45580</v>
+        <v>45965</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45527</v>
+        <v>46002</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6328,7 +6328,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45965</v>
+        <v>44965</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6415,10 +6415,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45338</v>
+        <v>45558</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6474,7 +6474,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44965</v>
+        <v>45063</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6547,7 +6547,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45527</v>
+        <v>45194</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6620,7 +6620,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6634,10 +6634,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44502</v>
+        <v>45519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6649,13 +6649,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6698,7 +6693,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6708,14 +6703,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45021</v>
+        <v>45775</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6728,7 +6723,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6771,7 +6766,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6785,10 +6780,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45960</v>
+        <v>44845</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6801,7 +6796,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6844,7 +6839,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6854,14 +6849,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46195</v>
+        <v>45034</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6874,7 +6869,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6917,7 +6912,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6931,10 +6926,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45194</v>
+        <v>44515</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6947,7 +6942,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6990,7 +6985,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7000,14 +6995,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45619</v>
+        <v>44922</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7020,7 +7015,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7063,7 +7058,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7077,10 +7072,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45775</v>
+        <v>46058</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7093,7 +7088,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7136,7 +7131,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7150,10 +7145,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45561</v>
+        <v>44574</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7166,7 +7161,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7209,7 +7204,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20813-2026</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7223,10 +7218,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46141</v>
+        <v>46195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7239,7 +7234,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7282,7 +7277,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7292,14 +7287,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45932</v>
+        <v>45253</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7312,7 +7307,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7355,7 +7350,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7369,10 +7364,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46002</v>
+        <v>45580</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7385,7 +7380,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7428,7 +7423,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7442,10 +7437,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46273</v>
+        <v>45757</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7458,7 +7453,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7501,7 +7496,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7515,10 +7510,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45166</v>
+        <v>46112</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7531,7 +7526,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7574,7 +7569,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7584,14 +7579,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44805</v>
+        <v>45049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7604,7 +7599,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7647,7 +7642,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7657,14 +7652,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44953</v>
+        <v>46125</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7677,7 +7672,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7720,7 +7715,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7730,14 +7725,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44953</v>
+        <v>45799</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7750,7 +7745,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7793,7 +7788,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7807,10 +7802,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46281</v>
+        <v>45754</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7823,7 +7818,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7866,7 +7861,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7880,10 +7875,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46281</v>
+        <v>45786</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7895,8 +7890,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7939,7 +7939,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7949,14 +7949,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45191</v>
+        <v>45203</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8012,7 +8012,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8026,10 +8026,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44755</v>
+        <v>44602</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8099,10 +8099,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45591</v>
+        <v>45251</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8158,7 +8158,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8172,10 +8172,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46282</v>
+        <v>44755</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8231,7 +8231,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46281</v>
+        <v>45591</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8304,7 +8304,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 20813-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44602</v>
+        <v>46141</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8377,7 +8377,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8387,14 +8387,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45107</v>
+        <v>45619</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8464,10 +8464,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46281</v>
+        <v>45719</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8523,7 +8523,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8533,14 +8533,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44922</v>
+        <v>44953</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45049</v>
+        <v>44953</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,7 +8669,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8679,14 +8679,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44922</v>
+        <v>45932</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,7 +8742,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8752,14 +8752,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44929</v>
+        <v>45229</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8815,7 +8815,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8829,10 +8829,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44991</v>
+        <v>45177</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8888,7 +8888,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46058</v>
+        <v>46273</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8961,7 +8961,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8971,14 +8971,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45394</v>
+        <v>45680</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9034,7 +9034,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45324</v>
+        <v>45617</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9107,7 +9107,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9117,14 +9117,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44984</v>
+        <v>46281</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9180,7 +9180,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44845</v>
+        <v>45666</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9253,7 +9253,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45251</v>
+        <v>45789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9326,7 +9326,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9340,10 +9340,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45253</v>
+        <v>45579</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9399,7 +9399,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44979</v>
+        <v>45709</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9472,7 +9472,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45617</v>
+        <v>46281</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9545,7 +9545,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45680</v>
+        <v>46281</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9632,10 +9632,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45789</v>
+        <v>46281</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9691,7 +9691,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45709</v>
+        <v>45720</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9764,7 +9764,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45666</v>
+        <v>46282</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9837,7 +9837,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45579</v>
+        <v>45820</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45720</v>
+        <v>45525</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9983,7 +9983,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9997,10 +9997,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10056,7 +10056,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10070,10 +10070,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>44944</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>46176</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>44690</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>44944</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>45825</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>44602</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>44734</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>44602</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>44804</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>44715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>44804</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44574</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>44851</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44515</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44502</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44922</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>45191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>44900</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44715</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>44929</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>44929</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>44805</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>44922</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45394</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45229</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>45338</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>45527</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>44901</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>44922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44502</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>45203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>44944</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45642</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>45280</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>45401</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45642</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45561</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45898</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>46000</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>44991</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>44984</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>45249</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>46146</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>45229</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45166</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45960</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>45239</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>45527</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>45324</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45965</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>46002</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>44965</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>45558</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>45063</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45194</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>45519</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>45775</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44845</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>45034</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44515</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>44922</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>46058</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44574</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>46195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45253</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45580</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45757</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>46112</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>45049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>46125</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>45799</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>45754</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45786</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>45203</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>44602</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8102,7 +8102,7 @@
         <v>45251</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>44755</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>45591</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>46141</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>45619</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45719</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>44953</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>44953</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>45932</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45229</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>45177</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>46273</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45680</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45617</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>46281</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>45666</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>45789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>45579</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>45709</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>46281</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>46281</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>46281</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>45720</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>46282</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45820</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45525</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>44715</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE126"/>
+  <dimension ref="A1:AE125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>44944</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1127,24 +1127,24 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25330-2026</t>
+          <t>S 2391-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46176</v>
+        <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1181,80 +1181,76 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Knärot
-Flagellkvastmossa</t>
+          <t>Blåsippa
+Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 25330-2026 artfynd.xlsx", "A 25330-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/S 2391-2022 artfynd.xlsx", "S 2391-2022")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 25330-2026 karta.png", "A 25330-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/S 2391-2022 karta.png", "S 2391-2022")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 25330-2026 georefererad karta.tif", "A 25330-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/S 2391-2022 georefererad karta.tif", "S 2391-2022")</f>
         <v/>
       </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 25330-2026 karta knärot.png", "A 25330-2026")</f>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/S 2391-2022 FSC-klagomål.docx", "S 2391-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 25330-2026 FSC-klagomål.docx", "A 25330-2026")</f>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/S 2391-2022 FSC-klagomål mail.docx", "S 2391-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 25330-2026 FSC-klagomål mail.docx", "A 25330-2026")</f>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/S 2391-2022 tillsynsbegäran.docx", "S 2391-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 25330-2026 tillsynsbegäran.docx", "A 25330-2026")</f>
-        <v/>
-      </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 25330-2026 tillsynsbegäran mail.docx", "A 25330-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/S 2391-2022 tillsynsbegäran mail.docx", "S 2391-2022")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S 2391-2022</t>
+          <t>A 56101-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44690</v>
+        <v>45973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1267,14 +1263,14 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -1297,53 +1293,52 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa
-Lopplummer (aggregat)</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/S 2391-2022 artfynd.xlsx", "S 2391-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/S 2391-2022 karta.png", "S 2391-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/S 2391-2022 georefererad karta.tif", "S 2391-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/S 2391-2022 FSC-klagomål.docx", "S 2391-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/S 2391-2022 FSC-klagomål mail.docx", "S 2391-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/S 2391-2022 tillsynsbegäran.docx", "S 2391-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/S 2391-2022 tillsynsbegäran mail.docx", "S 2391-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 56101-2025</t>
+          <t>A 2763-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45973</v>
+        <v>44944</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1373,13 +1368,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1413,42 +1408,42 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2763-2023</t>
+          <t>A 31382-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44944</v>
+        <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1478,7 +1473,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1518,42 +1513,42 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 31382-2026</t>
+          <t>A 29819-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1567,10 +1562,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46219</v>
+        <v>45825</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1583,7 +1578,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1619,46 +1614,50 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 29819-2025</t>
+          <t>A 6870-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1672,10 +1671,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45825</v>
+        <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1688,10 +1687,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1718,56 +1717,20 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 6870-2022</t>
+          <t>A 25943-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1777,14 +1740,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44602</v>
+        <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1797,7 +1760,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1840,7 +1803,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25943-2022</t>
+          <t>A 6871-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1850,14 +1813,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44734</v>
+        <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1870,7 +1833,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1913,7 +1876,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6871-2022</t>
+          <t>A 6800-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1930,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1943,7 +1906,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1986,7 +1949,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6800-2022</t>
+          <t>A 6822-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2003,7 +1966,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2016,7 +1979,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2076,7 +2039,7 @@
         <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2095,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 6822-2022</t>
+          <t>A 36402-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2146,10 +2109,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44602</v>
+        <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2161,8 +2124,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2205,7 +2173,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 36402-2022</t>
+          <t>A 64871-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2219,10 +2187,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44804</v>
+        <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2234,13 +2202,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2283,7 +2246,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 64871-2021</t>
+          <t>A 23080-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2297,10 +2260,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44512</v>
+        <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2313,7 +2276,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2356,7 +2319,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23080-2022</t>
+          <t>A 65112-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2370,10 +2333,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44715</v>
+        <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2386,7 +2349,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2429,7 +2392,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 65112-2021</t>
+          <t>A 36404-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2443,10 +2406,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44515</v>
+        <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2456,6 +2419,11 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -2502,7 +2470,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 36404-2022</t>
+          <t>A 1882-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2516,10 +2484,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44804</v>
+        <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2531,13 +2499,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2580,7 +2543,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 1882-2022</t>
+          <t>A 46707-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,10 +2557,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44574</v>
+        <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2610,7 +2573,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2653,7 +2616,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46707-2022</t>
+          <t>A 495-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2667,10 +2630,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44851</v>
+        <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,8 +2645,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2726,7 +2694,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 495-2022</t>
+          <t>A 496-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2743,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2761,7 +2729,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2804,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 496-2022</t>
+          <t>A 65095-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2818,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44566</v>
+        <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,13 +2801,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2882,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 65095-2021</t>
+          <t>A 61986-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2896,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44515</v>
+        <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2911,8 +2874,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2955,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61986-2021</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2969,10 +2937,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44502</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2984,13 +2952,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3033,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3047,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44922</v>
+        <v>44715</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3063,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3123,7 +3086,7 @@
         <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3159,7 @@
         <v>45191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3232,7 @@
         <v>45021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3305,7 @@
         <v>44900</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3378,7 @@
         <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3476,7 +3439,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3490,10 +3453,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44715</v>
+        <v>44960</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3506,7 +3469,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3549,7 +3512,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3559,14 +3522,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44960</v>
+        <v>44929</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3579,7 +3542,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3622,7 +3585,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3639,7 +3602,7 @@
         <v>44929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3652,7 +3615,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3695,7 +3658,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3712,7 +3675,7 @@
         <v>44929</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3725,7 +3688,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3768,7 +3731,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3782,10 +3745,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44929</v>
+        <v>44930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3798,7 +3761,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3841,7 +3804,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3851,14 +3814,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44930</v>
+        <v>44805</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3871,7 +3834,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3914,7 +3877,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3928,10 +3891,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44805</v>
+        <v>44922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3944,7 +3907,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3987,7 +3950,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4001,10 +3964,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44922</v>
+        <v>45229</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4017,7 +3980,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4060,7 +4023,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4070,14 +4033,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45394</v>
+        <v>45338</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4090,7 +4053,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4133,7 +4096,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4143,14 +4106,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45229</v>
+        <v>45394</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4163,7 +4126,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4206,7 +4169,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4220,10 +4183,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45338</v>
+        <v>45527</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4236,7 +4199,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4279,7 +4242,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4293,10 +4256,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45527</v>
+        <v>44901</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4309,7 +4272,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4352,7 +4315,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4366,10 +4329,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44901</v>
+        <v>44922</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4382,7 +4345,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4425,7 +4388,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4439,10 +4402,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44922</v>
+        <v>44502</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4454,8 +4417,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4498,7 +4466,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4512,10 +4480,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44502</v>
+        <v>45799</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4527,13 +4495,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4593,7 +4556,7 @@
         <v>45203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4649,7 +4612,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4663,10 +4626,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44944</v>
+        <v>45754</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4679,7 +4642,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4722,7 +4685,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4736,10 +4699,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45642</v>
+        <v>44944</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4752,7 +4715,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4795,7 +4758,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4809,10 +4772,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44979</v>
+        <v>45786</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4824,8 +4787,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4868,7 +4836,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4882,10 +4850,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45280</v>
+        <v>45642</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4898,7 +4866,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4941,7 +4909,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4955,10 +4923,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45401</v>
+        <v>45642</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4971,7 +4939,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5014,7 +4982,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5028,10 +4996,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45642</v>
+        <v>45280</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5044,7 +5012,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5087,7 +5055,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5097,14 +5065,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45561</v>
+        <v>45898</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5117,7 +5085,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5160,7 +5128,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5170,14 +5138,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45898</v>
+        <v>46000</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5190,7 +5158,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5233,7 +5201,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5247,10 +5215,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46000</v>
+        <v>44979</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5263,7 +5231,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5306,7 +5274,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5320,10 +5288,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44991</v>
+        <v>45401</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5336,7 +5304,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5379,7 +5347,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5389,14 +5357,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44984</v>
+        <v>45561</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5409,7 +5377,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5452,7 +5420,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5466,10 +5434,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45610</v>
+        <v>46146</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5482,7 +5450,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5525,7 +5493,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5539,10 +5507,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45249</v>
+        <v>44991</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5555,7 +5523,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.1</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5598,7 +5566,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5608,14 +5576,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46146</v>
+        <v>44984</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5628,7 +5596,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5671,7 +5639,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5685,10 +5653,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45754</v>
+        <v>45610</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5701,7 +5669,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5744,7 +5712,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5758,10 +5726,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45229</v>
+        <v>45960</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5774,7 +5742,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5817,7 +5785,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5831,10 +5799,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45166</v>
+        <v>45249</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5847,7 +5815,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5890,7 +5858,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5904,10 +5872,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45960</v>
+        <v>45754</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5920,7 +5888,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5963,7 +5931,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5977,10 +5945,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45239</v>
+        <v>45965</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5993,7 +5961,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6036,7 +6004,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6050,10 +6018,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45527</v>
+        <v>45229</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6066,7 +6034,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6109,7 +6077,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6123,10 +6091,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45324</v>
+        <v>45166</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6139,7 +6107,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6182,7 +6150,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6196,10 +6164,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45965</v>
+        <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6212,7 +6180,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6255,7 +6223,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6269,10 +6237,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46002</v>
+        <v>45239</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6285,7 +6253,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6328,7 +6296,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6342,10 +6310,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44965</v>
+        <v>45527</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6358,7 +6326,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6401,7 +6369,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6415,10 +6383,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45558</v>
+        <v>45324</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6431,7 +6399,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6474,7 +6442,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6488,10 +6456,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45063</v>
+        <v>46195</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6504,7 +6472,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6547,7 +6515,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6561,10 +6529,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45194</v>
+        <v>46058</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6577,7 +6545,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6620,7 +6588,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6634,10 +6602,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45519</v>
+        <v>44965</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6650,7 +6618,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6693,7 +6661,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6707,10 +6675,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45775</v>
+        <v>45558</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6723,7 +6691,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6766,7 +6734,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6780,10 +6748,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44845</v>
+        <v>45063</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6796,7 +6764,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6839,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6849,14 +6817,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45034</v>
+        <v>45194</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6869,7 +6837,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6912,7 +6880,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6926,10 +6894,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44515</v>
+        <v>45519</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6942,7 +6910,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6985,7 +6953,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6999,10 +6967,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44922</v>
+        <v>45775</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7015,7 +6983,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7058,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7072,10 +7040,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46058</v>
+        <v>44845</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7088,7 +7056,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7131,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7141,14 +7109,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44574</v>
+        <v>45034</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7161,7 +7129,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7204,7 +7172,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7218,10 +7186,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46195</v>
+        <v>46112</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7234,7 +7202,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7277,7 +7245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7291,10 +7259,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45253</v>
+        <v>44515</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7307,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7350,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7364,10 +7332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45580</v>
+        <v>44922</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7380,7 +7348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7423,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7437,10 +7405,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45757</v>
+        <v>46125</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7453,7 +7421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7496,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7510,10 +7478,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46112</v>
+        <v>44574</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7526,7 +7494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7569,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7579,14 +7547,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45049</v>
+        <v>45253</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7599,7 +7567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7642,7 +7610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7656,10 +7624,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46125</v>
+        <v>45580</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7672,7 +7640,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7715,7 +7683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7729,10 +7697,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45799</v>
+        <v>45757</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7745,7 +7713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7788,7 +7756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7798,14 +7766,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45754</v>
+        <v>45932</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7818,7 +7786,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7861,7 +7829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7871,14 +7839,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45786</v>
+        <v>45049</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7890,13 +7858,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7939,7 +7902,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7949,14 +7912,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45203</v>
+        <v>46273</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7969,7 +7932,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8012,7 +7975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8022,14 +7985,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44602</v>
+        <v>45203</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8042,7 +8005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8085,7 +8048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8099,10 +8062,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45251</v>
+        <v>44602</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8115,7 +8078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8158,7 +8121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8172,10 +8135,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44755</v>
+        <v>45251</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8188,7 +8151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8231,7 +8194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8245,10 +8208,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45591</v>
+        <v>44755</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8261,7 +8224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8304,7 +8267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20813-2026</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8318,10 +8281,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46141</v>
+        <v>46281</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8334,7 +8297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8377,7 +8340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8387,14 +8350,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45619</v>
+        <v>45591</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8407,7 +8370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8450,7 +8413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8464,10 +8427,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45719</v>
+        <v>46281</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8480,7 +8443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8523,7 +8486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8533,14 +8496,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44953</v>
+        <v>46281</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8553,7 +8516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8596,7 +8559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8606,14 +8569,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44953</v>
+        <v>46281</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8626,7 +8589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8669,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8683,10 +8646,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45932</v>
+        <v>45619</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8699,7 +8662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8742,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8756,10 +8719,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45229</v>
+        <v>46282</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8772,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8815,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8829,10 +8792,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45177</v>
+        <v>45719</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8845,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8888,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8898,14 +8861,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46273</v>
+        <v>44953</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8918,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8961,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8971,14 +8934,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45680</v>
+        <v>44953</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8991,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9034,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9048,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45617</v>
+        <v>46286</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9064,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9107,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9121,10 +9084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46281</v>
+        <v>45229</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9137,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9180,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9194,10 +9157,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45666</v>
+        <v>45177</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9253,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9267,10 +9230,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45789</v>
+        <v>45680</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9283,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9326,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9340,10 +9303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45579</v>
+        <v>45617</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9356,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.8</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9399,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9413,10 +9376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45709</v>
+        <v>45666</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9429,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9472,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9486,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46281</v>
+        <v>45789</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9502,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9545,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9559,10 +9522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46281</v>
+        <v>45579</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9575,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9618,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9632,10 +9595,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46281</v>
+        <v>45709</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9648,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9708,7 +9671,7 @@
         <v>45720</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9764,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9778,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46282</v>
+        <v>45820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9794,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9837,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9851,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45820</v>
+        <v>45525</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9867,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>7.8</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9910,24 +9873,24 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45525</v>
+        <v>45222</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9940,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9980,10 +9943,10 @@
       </c>
       <c r="V124" s="2" t="inlineStr"/>
     </row>
-    <row r="125" ht="15" customHeight="1">
+    <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9997,10 +9960,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10013,7 +9976,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10052,79 +10015,6 @@
         <v>0</v>
       </c>
       <c r="V125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>S 3071-2022</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="n">
-        <v>44715</v>
-      </c>
-      <c r="E126" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I126" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 417-2023</t>
+          <t>A 2764-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44929</v>
+        <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Ask
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 417-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Nattskärra
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 2764-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2763-2023</t>
+          <t>A 29819-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44944</v>
+        <v>45825</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1404,256 +1404,256 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 2763-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 31382-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>46219</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>1.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 29819-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45825</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6822-2022</t>
+          <t>A 10328-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44602</v>
+        <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10328-2022</t>
+          <t>A 6822-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44623</v>
+        <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 65095-2021</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44515</v>
+        <v>45177</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61986-2021</t>
+          <t>A 65095-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44502</v>
+        <v>44515</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2874,13 +2874,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2923,7 +2918,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2933,14 +2928,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2953,7 +2948,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2996,7 +2991,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3006,14 +3001,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44715</v>
+        <v>44929</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3026,7 +3021,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3069,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45107</v>
+        <v>45229</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 61986-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45191</v>
+        <v>44502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3171,8 +3166,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45021</v>
+        <v>45789</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44900</v>
+        <v>44515</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44986</v>
+        <v>45719</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3390,13 +3390,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3439,7 +3434,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3453,10 +3448,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44960</v>
+        <v>45401</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3469,7 +3464,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3512,7 +3507,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3522,14 +3517,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44929</v>
+        <v>45709</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3542,7 +3537,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3585,7 +3580,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3595,14 +3590,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44929</v>
+        <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3615,7 +3610,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3658,7 +3653,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3668,14 +3663,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44929</v>
+        <v>45579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3688,7 +3683,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3731,7 +3726,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3741,14 +3736,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44930</v>
+        <v>45249</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3761,7 +3756,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3804,7 +3799,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3818,10 +3813,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44805</v>
+        <v>45720</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3834,7 +3829,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3877,7 +3872,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3891,10 +3886,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44922</v>
+        <v>45757</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3907,7 +3902,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3950,7 +3945,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3964,10 +3959,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45229</v>
+        <v>45754</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3980,7 +3975,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4023,7 +4018,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4033,14 +4028,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45338</v>
+        <v>45203</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4053,7 +4048,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4096,7 +4091,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4106,14 +4101,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45394</v>
+        <v>44901</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4126,7 +4121,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4169,7 +4164,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4183,10 +4178,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45527</v>
+        <v>45229</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4199,7 +4194,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4242,7 +4237,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4256,10 +4251,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44901</v>
+        <v>45229</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4272,7 +4267,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4315,7 +4310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4329,10 +4324,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44922</v>
+        <v>45580</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4345,7 +4340,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4388,7 +4383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44502</v>
+        <v>45642</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4417,13 +4412,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4466,7 +4456,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4476,14 +4466,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45799</v>
+        <v>45898</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4496,7 +4486,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4539,7 +4529,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4549,14 +4539,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45203</v>
+        <v>45527</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4569,7 +4559,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4612,7 +4602,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4626,10 +4616,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45754</v>
+        <v>45338</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4685,7 +4675,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4699,10 +4689,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44944</v>
+        <v>44965</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4715,7 +4705,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4758,7 +4748,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4772,10 +4762,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45786</v>
+        <v>45239</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4787,13 +4777,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4836,7 +4821,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4850,10 +4835,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45642</v>
+        <v>44944</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4866,7 +4851,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4909,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4923,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45642</v>
+        <v>44922</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4939,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4982,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4996,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45280</v>
+        <v>45527</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5012,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5055,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5065,14 +5050,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45898</v>
+        <v>44502</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5084,8 +5069,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5128,7 +5118,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5138,14 +5128,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46000</v>
+        <v>44929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5158,7 +5148,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5201,7 +5191,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5211,14 +5201,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44979</v>
+        <v>45203</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5274,7 +5264,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5288,10 +5278,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45401</v>
+        <v>45519</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5304,7 +5294,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5347,7 +5337,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5361,10 +5351,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45561</v>
+        <v>45063</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5377,7 +5367,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5420,7 +5410,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5434,10 +5424,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46146</v>
+        <v>44574</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5450,7 +5440,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5493,7 +5483,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5507,10 +5497,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44991</v>
+        <v>45558</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5523,7 +5513,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5566,7 +5556,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5580,10 +5570,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44984</v>
+        <v>45021</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5596,7 +5586,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5639,7 +5629,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5653,10 +5643,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45610</v>
+        <v>44922</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5669,7 +5659,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5712,7 +5702,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5726,10 +5716,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45960</v>
+        <v>44986</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5741,8 +5731,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5785,7 +5780,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5799,10 +5794,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45249</v>
+        <v>45960</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5815,7 +5810,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5858,7 +5853,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5872,10 +5867,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45754</v>
+        <v>45194</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5888,7 +5883,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5931,7 +5926,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5941,14 +5936,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45965</v>
+        <v>45619</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5961,7 +5956,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6004,7 +5999,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6018,10 +6013,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45229</v>
+        <v>45820</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6034,7 +6029,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6077,7 +6072,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6091,10 +6086,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45166</v>
+        <v>45775</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6107,7 +6102,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6150,7 +6145,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6164,10 +6159,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46002</v>
+        <v>45561</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6180,7 +6175,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6223,7 +6218,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6237,10 +6232,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45239</v>
+        <v>44960</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6253,7 +6248,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6296,7 +6291,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6306,14 +6301,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45527</v>
+        <v>45034</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6326,7 +6321,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6369,7 +6364,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6383,10 +6378,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45324</v>
+        <v>44900</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6399,7 +6394,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6442,7 +6437,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6456,10 +6451,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46195</v>
+        <v>44715</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6472,7 +6467,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6515,7 +6510,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6529,10 +6524,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46058</v>
+        <v>45610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6545,7 +6540,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6588,7 +6583,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6602,10 +6597,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44965</v>
+        <v>46002</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6618,7 +6613,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6661,7 +6656,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6675,10 +6670,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45558</v>
+        <v>46286</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6691,7 +6686,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6734,7 +6729,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6748,10 +6743,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45063</v>
+        <v>46058</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6764,7 +6759,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6802,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6821,10 +6816,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45194</v>
+        <v>45166</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6837,7 +6832,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6880,7 +6875,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6894,10 +6889,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45519</v>
+        <v>44805</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6910,7 +6905,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6953,7 +6948,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6963,14 +6958,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45775</v>
+        <v>44953</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6983,7 +6978,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7021,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7036,14 +7031,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44845</v>
+        <v>44953</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7051,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7094,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7109,14 +7104,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45034</v>
+        <v>45191</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7129,7 +7124,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7172,7 +7167,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7186,10 +7181,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46112</v>
+        <v>44755</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7202,7 +7197,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7245,7 +7240,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7259,10 +7254,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44515</v>
+        <v>45591</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7270,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7313,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7332,10 +7327,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44922</v>
+        <v>44602</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7348,7 +7343,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7386,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7405,10 +7400,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46125</v>
+        <v>45107</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7421,7 +7416,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7464,7 +7459,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7478,10 +7473,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44574</v>
+        <v>44922</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7494,7 +7489,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7537,7 +7532,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7547,14 +7542,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45253</v>
+        <v>45049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7567,7 +7562,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7610,7 +7605,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7624,10 +7619,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45580</v>
+        <v>45525</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7640,7 +7635,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7683,7 +7678,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7697,10 +7692,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45757</v>
+        <v>46112</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7713,7 +7708,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7756,7 +7751,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7766,14 +7761,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45932</v>
+        <v>46125</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7786,7 +7781,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7829,7 +7824,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7839,14 +7834,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45049</v>
+        <v>44922</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7859,7 +7854,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7902,7 +7897,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7912,14 +7907,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46273</v>
+        <v>44929</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7932,7 +7927,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7975,7 +7970,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7985,14 +7980,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45203</v>
+        <v>44991</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8005,7 +8000,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8048,7 +8043,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8062,10 +8057,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44602</v>
+        <v>45754</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8078,7 +8073,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8121,7 +8116,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8131,14 +8126,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45251</v>
+        <v>45394</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8151,7 +8146,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8194,7 +8189,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8208,10 +8203,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44755</v>
+        <v>45324</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8224,7 +8219,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8267,7 +8262,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8281,10 +8276,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46281</v>
+        <v>46000</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8297,7 +8292,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8340,7 +8335,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8354,10 +8349,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45591</v>
+        <v>45799</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8370,7 +8365,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8413,7 +8408,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8423,14 +8418,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46281</v>
+        <v>44984</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8443,7 +8438,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8486,7 +8481,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8500,10 +8495,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46281</v>
+        <v>45280</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8516,7 +8511,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8559,7 +8554,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8573,10 +8568,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46281</v>
+        <v>44845</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8589,7 +8584,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8632,7 +8627,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8642,14 +8637,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45619</v>
+        <v>45786</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8661,8 +8656,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46282</v>
+        <v>45642</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8792,10 +8792,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45719</v>
+        <v>45251</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8861,14 +8861,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44953</v>
+        <v>45253</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8934,14 +8934,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44953</v>
+        <v>44979</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46286</v>
+        <v>46146</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45229</v>
+        <v>45617</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9157,10 +9157,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45177</v>
+        <v>45680</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45680</v>
+        <v>45965</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45617</v>
+        <v>46195</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9372,14 +9372,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45666</v>
+        <v>45932</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45789</v>
+        <v>46273</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45579</v>
+        <v>46281</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45709</v>
+        <v>46281</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45720</v>
+        <v>46282</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45820</v>
+        <v>46281</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>7.8</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9800,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45525</v>
+        <v>46281</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9873,7 +9873,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9887,10 +9887,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9946,7 +9946,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 2764-2023</t>
+          <t>A 417-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44944</v>
+        <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2764-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Ask
 Vårstarr</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 417-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 29819-2025</t>
+          <t>A 2763-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45825</v>
+        <v>44944</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1404,256 +1404,256 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31382-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 29819-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45825</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Nattskärra</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 2763-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31382-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 65095-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45177</v>
+        <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 65095-2021</t>
+          <t>A 61986-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44515</v>
+        <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2874,8 +2874,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2918,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2928,14 +2933,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44930</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2948,7 +2953,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2991,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3001,14 +3006,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44929</v>
+        <v>44715</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3021,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45229</v>
+        <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61986-2021</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3156,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44502</v>
+        <v>45191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3166,13 +3171,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45789</v>
+        <v>45021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44515</v>
+        <v>44900</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45719</v>
+        <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3390,8 +3390,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3434,7 +3439,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3448,10 +3453,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45401</v>
+        <v>44960</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3464,7 +3469,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3507,7 +3512,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3517,14 +3522,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45709</v>
+        <v>44929</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3537,7 +3542,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3580,7 +3585,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3590,14 +3595,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45666</v>
+        <v>44929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3610,7 +3615,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3653,7 +3658,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3663,14 +3668,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45579</v>
+        <v>44929</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3683,7 +3688,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3726,7 +3731,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3736,14 +3741,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45249</v>
+        <v>44930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3756,7 +3761,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3799,7 +3804,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3813,10 +3818,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45720</v>
+        <v>44805</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3829,7 +3834,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3872,7 +3877,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3886,10 +3891,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45757</v>
+        <v>44922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3902,7 +3907,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3945,7 +3950,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3955,14 +3960,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45754</v>
+        <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3975,7 +3980,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4018,7 +4023,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4028,14 +4033,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45203</v>
+        <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4048,7 +4053,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4091,7 +4096,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4105,10 +4110,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44901</v>
+        <v>45338</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4121,7 +4126,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4164,7 +4169,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4178,10 +4183,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45229</v>
+        <v>45527</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4194,7 +4199,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4237,7 +4242,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4251,10 +4256,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45229</v>
+        <v>44901</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4267,7 +4272,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4310,7 +4315,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4324,10 +4329,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45580</v>
+        <v>45799</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4340,7 +4345,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4383,7 +4388,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45642</v>
+        <v>44922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4413,7 +4418,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4456,7 +4461,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4466,14 +4471,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45898</v>
+        <v>45754</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4486,7 +4491,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4529,7 +4534,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4543,10 +4548,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45527</v>
+        <v>44502</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4558,8 +4563,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4602,7 +4612,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4612,14 +4622,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45338</v>
+        <v>45203</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4632,7 +4642,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4675,7 +4685,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4689,10 +4699,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44965</v>
+        <v>45786</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4704,8 +4714,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4748,7 +4763,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4762,10 +4777,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45239</v>
+        <v>44944</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4778,7 +4793,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4821,7 +4836,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4835,10 +4850,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44944</v>
+        <v>45642</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4851,7 +4866,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4909,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4904,14 +4919,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44922</v>
+        <v>45898</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4939,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4982,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4981,10 +4996,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45527</v>
+        <v>45642</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +5012,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5055,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5069,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44502</v>
+        <v>44979</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5069,13 +5084,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5118,7 +5128,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5128,14 +5138,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44929</v>
+        <v>45401</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5148,7 +5158,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5191,7 +5201,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5201,14 +5211,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45203</v>
+        <v>45561</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5221,7 +5231,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5264,7 +5274,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5278,10 +5288,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45519</v>
+        <v>45280</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5294,7 +5304,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5337,7 +5347,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5351,10 +5361,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45063</v>
+        <v>44991</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5367,7 +5377,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5410,7 +5420,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5420,14 +5430,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44574</v>
+        <v>44984</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5440,7 +5450,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5483,7 +5493,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5497,10 +5507,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45558</v>
+        <v>45610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5513,7 +5523,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5556,7 +5566,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5566,14 +5576,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45021</v>
+        <v>46000</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5586,7 +5596,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5629,7 +5639,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5643,10 +5653,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44922</v>
+        <v>45249</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5659,7 +5669,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>6.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5702,7 +5712,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5716,10 +5726,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44986</v>
+        <v>45960</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5731,13 +5741,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5780,7 +5785,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5794,10 +5799,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45960</v>
+        <v>45754</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5810,7 +5815,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5853,7 +5858,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5867,10 +5872,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45194</v>
+        <v>45229</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5883,7 +5888,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5926,7 +5931,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5936,14 +5941,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45619</v>
+        <v>45166</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5956,7 +5961,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5999,7 +6004,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6013,10 +6018,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45820</v>
+        <v>46146</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6029,7 +6034,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.8</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6072,7 +6077,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6086,10 +6091,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45775</v>
+        <v>45239</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6102,7 +6107,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6145,7 +6150,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6159,10 +6164,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45561</v>
+        <v>46002</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6175,7 +6180,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6218,7 +6223,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6232,10 +6237,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44960</v>
+        <v>45527</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6248,7 +6253,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6291,7 +6296,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6301,14 +6306,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45034</v>
+        <v>45324</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6321,7 +6326,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6364,7 +6369,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6378,10 +6383,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44900</v>
+        <v>45965</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6394,7 +6399,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6437,7 +6442,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6451,10 +6456,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44715</v>
+        <v>44965</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6467,7 +6472,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6510,7 +6515,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6524,10 +6529,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45610</v>
+        <v>45558</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6540,7 +6545,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6583,7 +6588,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6597,10 +6602,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46002</v>
+        <v>46058</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6613,7 +6618,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6656,7 +6661,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6670,10 +6675,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46286</v>
+        <v>45063</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6686,7 +6691,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6729,7 +6734,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6743,10 +6748,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46058</v>
+        <v>45194</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6759,7 +6764,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6802,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6816,10 +6821,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45166</v>
+        <v>45519</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6832,7 +6837,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6875,7 +6880,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6889,10 +6894,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44805</v>
+        <v>45775</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6905,7 +6910,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6948,7 +6953,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6958,14 +6963,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44953</v>
+        <v>44845</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6978,7 +6983,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7021,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7035,10 +7040,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44953</v>
+        <v>45034</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7051,7 +7056,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7094,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7108,10 +7113,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45191</v>
+        <v>44515</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7124,7 +7129,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7167,7 +7172,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7181,10 +7186,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44755</v>
+        <v>44922</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7197,7 +7202,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7240,7 +7245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7254,10 +7259,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45591</v>
+        <v>46112</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7270,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7313,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7327,10 +7332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44602</v>
+        <v>46125</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7343,7 +7348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7386,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7400,10 +7405,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45107</v>
+        <v>44574</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7416,7 +7421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7459,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7473,10 +7478,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44922</v>
+        <v>46195</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7489,7 +7494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7532,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7542,14 +7547,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45049</v>
+        <v>45253</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7562,7 +7567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7605,7 +7610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7619,10 +7624,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45525</v>
+        <v>45580</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7635,7 +7640,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7678,7 +7683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7692,10 +7697,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46112</v>
+        <v>45757</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7708,7 +7713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7751,7 +7756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7761,14 +7766,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46125</v>
+        <v>45049</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7781,7 +7786,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7824,7 +7829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7834,14 +7839,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44922</v>
+        <v>45932</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7854,7 +7859,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7897,7 +7902,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7911,10 +7916,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44929</v>
+        <v>45203</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7927,7 +7932,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7970,7 +7975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7984,10 +7989,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44991</v>
+        <v>44602</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8000,7 +8005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8043,7 +8048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8057,10 +8062,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45754</v>
+        <v>45251</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8073,7 +8078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8116,7 +8121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8126,14 +8131,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45394</v>
+        <v>44755</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8146,7 +8151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8189,7 +8194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8203,10 +8208,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45324</v>
+        <v>45591</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8219,7 +8224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8262,7 +8267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8272,14 +8277,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46000</v>
+        <v>45619</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8292,7 +8297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8335,7 +8340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8349,10 +8354,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45799</v>
+        <v>46273</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8365,7 +8370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8408,7 +8413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8418,14 +8423,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44984</v>
+        <v>45719</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8438,7 +8443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8481,7 +8486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8491,14 +8496,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45280</v>
+        <v>44953</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8511,7 +8516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8554,7 +8559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8564,14 +8569,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44845</v>
+        <v>44953</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8584,7 +8589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8627,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8641,10 +8646,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45786</v>
+        <v>45229</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8656,13 +8661,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45642</v>
+        <v>46281</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8792,10 +8792,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45251</v>
+        <v>46281</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45253</v>
+        <v>46281</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44979</v>
+        <v>46281</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46146</v>
+        <v>45177</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45617</v>
+        <v>46282</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>45680</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45965</v>
+        <v>45617</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46195</v>
+        <v>46286</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9372,14 +9372,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45932</v>
+        <v>45666</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46273</v>
+        <v>45789</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46281</v>
+        <v>45579</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46281</v>
+        <v>45709</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46282</v>
+        <v>45720</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46281</v>
+        <v>45820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>7.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9800,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46281</v>
+        <v>45525</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9873,7 +9873,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9887,10 +9887,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9946,7 +9946,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 417-2023</t>
+          <t>A 2764-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44929</v>
+        <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Ask
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 417-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Nattskärra
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 2764-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2763-2023</t>
+          <t>A 29819-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44944</v>
+        <v>45825</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1404,39 +1404,43 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
         <v/>
       </c>
     </row>
@@ -1460,7 +1464,7 @@
         <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1548,7 +1552,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 29819-2025</t>
+          <t>A 2763-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1562,10 +1566,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45825</v>
+        <v>44944</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1578,7 +1582,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1614,43 +1618,39 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>44515</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44715</v>
+        <v>45401</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45107</v>
+        <v>45229</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45191</v>
+        <v>44901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45021</v>
+        <v>45720</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44900</v>
+        <v>45239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44986</v>
+        <v>44944</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3390,13 +3390,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3439,7 +3434,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3453,10 +3448,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44960</v>
+        <v>44922</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3469,7 +3464,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3512,7 +3507,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3522,14 +3517,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44929</v>
+        <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3542,7 +3537,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3602,7 +3597,7 @@
         <v>44929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3658,7 +3653,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3672,10 +3667,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44929</v>
+        <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3688,7 +3683,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3731,7 +3726,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3745,10 +3740,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44930</v>
+        <v>45203</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3761,7 +3756,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3804,7 +3799,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3818,10 +3813,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44805</v>
+        <v>45519</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3834,7 +3829,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3877,7 +3872,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3891,10 +3886,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44922</v>
+        <v>45063</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3907,7 +3902,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3950,7 +3945,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3960,14 +3955,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45394</v>
+        <v>44574</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3980,7 +3975,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4023,7 +4018,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4037,10 +4032,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45229</v>
+        <v>45558</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4053,7 +4048,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4096,7 +4091,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4110,10 +4105,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45338</v>
+        <v>44922</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4126,7 +4121,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4169,7 +4164,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4183,10 +4178,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45527</v>
+        <v>44986</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4198,8 +4193,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44901</v>
+        <v>46112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45799</v>
+        <v>45960</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44922</v>
+        <v>46125</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45754</v>
+        <v>44960</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4544,14 +4544,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44502</v>
+        <v>45034</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4563,13 +4563,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4612,7 +4607,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4622,14 +4617,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45203</v>
+        <v>44900</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4642,7 +4637,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4685,7 +4680,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4699,10 +4694,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45786</v>
+        <v>44715</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4714,13 +4709,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4763,7 +4753,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4777,10 +4767,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44944</v>
+        <v>45610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4793,7 +4783,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4836,7 +4826,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4850,10 +4840,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45642</v>
+        <v>45177</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4866,7 +4856,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4909,7 +4899,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4919,14 +4909,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45898</v>
+        <v>45754</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4939,7 +4929,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4982,7 +4972,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4996,10 +4986,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45642</v>
+        <v>46000</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5012,7 +5002,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5055,7 +5045,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5069,10 +5059,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44979</v>
+        <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5085,7 +5075,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5128,7 +5118,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5142,10 +5132,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45401</v>
+        <v>45280</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5158,7 +5148,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5201,7 +5191,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5211,14 +5201,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45561</v>
+        <v>44930</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5231,7 +5221,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5274,7 +5264,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5284,14 +5274,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45280</v>
+        <v>44929</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5304,7 +5294,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5347,7 +5337,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5361,10 +5351,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44991</v>
+        <v>46002</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5377,7 +5367,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5420,7 +5410,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5430,14 +5420,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44984</v>
+        <v>45786</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5449,8 +5439,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5493,7 +5488,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5507,10 +5502,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45610</v>
+        <v>45642</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5523,7 +5518,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5566,7 +5561,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5580,10 +5575,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46000</v>
+        <v>45719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5596,7 +5591,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5639,7 +5634,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5653,10 +5648,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45249</v>
+        <v>45820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5669,7 +5664,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5712,7 +5707,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5726,10 +5721,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45960</v>
+        <v>45249</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5742,7 +5737,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5785,7 +5780,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5799,10 +5794,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45754</v>
+        <v>46146</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5858,7 +5853,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5872,10 +5867,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45229</v>
+        <v>45757</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5888,7 +5883,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5931,7 +5926,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5945,10 +5940,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45166</v>
+        <v>45754</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5961,7 +5956,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6004,7 +5999,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6014,14 +6009,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46146</v>
+        <v>45203</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6034,7 +6029,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6077,7 +6072,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6091,10 +6086,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45239</v>
+        <v>45229</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6107,7 +6102,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6150,7 +6145,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6164,10 +6159,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46002</v>
+        <v>45229</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6180,7 +6175,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6223,7 +6218,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6237,10 +6232,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45527</v>
+        <v>45580</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6253,7 +6248,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6296,7 +6291,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45324</v>
+        <v>45965</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6326,7 +6321,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6369,7 +6364,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6383,10 +6378,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45965</v>
+        <v>45527</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6399,7 +6394,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6442,7 +6437,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6456,10 +6451,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44965</v>
+        <v>45338</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6472,7 +6467,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6515,7 +6510,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6529,10 +6524,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45558</v>
+        <v>44965</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6545,7 +6540,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6588,7 +6583,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6602,10 +6597,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46058</v>
+        <v>45525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6618,7 +6613,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6661,7 +6656,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6675,10 +6670,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45063</v>
+        <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6691,7 +6686,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6734,7 +6729,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6748,10 +6743,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45194</v>
+        <v>44502</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6763,8 +6758,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45519</v>
+        <v>45021</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45775</v>
+        <v>46195</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44845</v>
+        <v>45194</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45034</v>
+        <v>45619</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44515</v>
+        <v>45775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7182,14 +7182,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44922</v>
+        <v>45932</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46112</v>
+        <v>45561</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46125</v>
+        <v>46273</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44574</v>
+        <v>46281</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46195</v>
+        <v>46281</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7537,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45253</v>
+        <v>46282</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7610,7 +7610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45580</v>
+        <v>46281</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7683,7 +7683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45757</v>
+        <v>46281</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7766,14 +7766,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45049</v>
+        <v>45166</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7829,7 +7829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7839,14 +7839,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45932</v>
+        <v>46286</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7902,7 +7902,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7912,14 +7912,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45203</v>
+        <v>44805</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7985,14 +7985,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44602</v>
+        <v>44953</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8048,7 +8048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8058,14 +8058,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45251</v>
+        <v>44953</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8121,7 +8121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44755</v>
+        <v>45191</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45591</v>
+        <v>44755</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8277,14 +8277,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45619</v>
+        <v>45591</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46273</v>
+        <v>44602</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8413,7 +8413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45719</v>
+        <v>45107</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8496,14 +8496,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44953</v>
+        <v>46058</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8569,14 +8569,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44953</v>
+        <v>44922</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8642,14 +8642,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45229</v>
+        <v>45049</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46281</v>
+        <v>44922</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8788,14 +8788,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46281</v>
+        <v>44929</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46281</v>
+        <v>44991</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8934,14 +8934,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46281</v>
+        <v>45394</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45177</v>
+        <v>45324</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9080,14 +9080,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46282</v>
+        <v>44984</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9157,10 +9157,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45680</v>
+        <v>44845</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45617</v>
+        <v>45251</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46286</v>
+        <v>45253</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45666</v>
+        <v>44979</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45789</v>
+        <v>45617</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45579</v>
+        <v>45680</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45709</v>
+        <v>45789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45720</v>
+        <v>45709</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45820</v>
+        <v>45666</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>7.8</v>
+        <v>2.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9800,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45525</v>
+        <v>45579</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9873,7 +9873,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9887,10 +9887,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9946,7 +9946,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44929</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>45825</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>44944</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44515</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45401</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45229</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45720</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44944</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>44922</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45203</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45519</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45063</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44574</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45558</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>44922</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44986</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45960</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>46125</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44960</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>45034</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44900</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44715</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45177</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>45754</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>46000</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>45280</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44930</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>44929</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46002</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45786</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45642</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45249</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>46146</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45757</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45754</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45203</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45229</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45229</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>45580</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45965</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45527</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>45338</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44965</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>44502</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45021</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>46195</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>45194</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>45619</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45932</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>45561</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>46273</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46281</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>46281</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>46282</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>46281</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>46281</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45166</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>46286</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>44805</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44953</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>44953</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45191</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>44755</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>45591</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44602</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45107</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>46058</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>44922</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45049</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>44922</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44929</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44991</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>45394</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>45324</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44984</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44845</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>45251</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>45253</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>44979</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45617</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>45680</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>45789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45709</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45666</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45579</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44715</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44929</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>45825</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>44944</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44515</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45401</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45229</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45720</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45239</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44944</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>44922</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45203</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>45519</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>45063</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44574</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45558</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>44922</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44986</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45960</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>46125</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44960</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>45034</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44900</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44715</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45610</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45177</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>45754</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>46000</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>45799</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>45280</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44930</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>44929</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>46002</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45786</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45642</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45249</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>46146</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45757</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45754</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45203</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45229</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45229</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>45580</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45965</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45527</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>45338</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44965</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>45525</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>44502</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45021</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>46195</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>45194</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>45619</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45932</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>45561</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>46273</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46281</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>46281</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>46282</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>46281</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>46281</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45166</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>46286</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>44805</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44953</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>44953</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45191</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>44755</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>45591</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44602</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45107</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>46058</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>44922</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45049</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>44922</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44929</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44991</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>45394</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>45324</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44984</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44845</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>45251</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>45253</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>44979</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45617</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>45680</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>45789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45709</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45666</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45579</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44715</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 2764-2023</t>
+          <t>A 417-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44944</v>
+        <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2764-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Ask
 Vårstarr</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 417-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 56101-2025</t>
+          <t>A 29819-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45973</v>
+        <v>45825</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1299,155 +1299,155 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 56101-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Hasselticka</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 29819-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45825</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31382-2026</t>
+          <t>A 2763-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46219</v>
+        <v>44944</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1517,143 +1517,143 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31382-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 2763-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44515</v>
+        <v>44715</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45401</v>
+        <v>44922</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45229</v>
+        <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44901</v>
+        <v>45191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45720</v>
+        <v>45021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45239</v>
+        <v>44900</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44944</v>
+        <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3390,8 +3390,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3434,7 +3439,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3448,10 +3453,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44922</v>
+        <v>46002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3464,7 +3469,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3507,7 +3512,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3521,10 +3526,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45642</v>
+        <v>45666</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3537,7 +3542,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3580,7 +3585,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3590,14 +3595,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44929</v>
+        <v>45789</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3610,7 +3615,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3653,7 +3658,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3663,14 +3668,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45898</v>
+        <v>45579</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3683,7 +3688,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3726,7 +3731,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3736,14 +3741,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45203</v>
+        <v>45709</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3756,7 +3761,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3799,7 +3804,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3813,10 +3818,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45519</v>
+        <v>44960</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3829,7 +3834,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3872,7 +3877,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3882,14 +3887,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45063</v>
+        <v>44929</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3902,7 +3907,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3945,7 +3950,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3955,14 +3960,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44574</v>
+        <v>44929</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3975,7 +3980,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4018,7 +4023,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4032,10 +4037,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45558</v>
+        <v>45720</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4048,7 +4053,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4091,7 +4096,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4105,10 +4110,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44922</v>
+        <v>45642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4121,7 +4126,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4164,7 +4169,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4174,14 +4179,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44986</v>
+        <v>45898</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4191,11 +4196,6 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -4242,7 +4242,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4252,14 +4252,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46112</v>
+        <v>44929</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4325,14 +4325,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45960</v>
+        <v>44930</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46125</v>
+        <v>44805</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44960</v>
+        <v>45820</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4544,14 +4544,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45034</v>
+        <v>44922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44900</v>
+        <v>45525</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4690,14 +4690,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44715</v>
+        <v>45394</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45610</v>
+        <v>45960</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45177</v>
+        <v>45229</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4899,7 +4899,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45754</v>
+        <v>45338</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46000</v>
+        <v>45527</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5045,7 +5045,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45799</v>
+        <v>44901</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45280</v>
+        <v>44922</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5191,7 +5191,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5201,14 +5201,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44930</v>
+        <v>44502</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5220,8 +5220,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5264,7 +5269,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5278,10 +5283,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44929</v>
+        <v>45203</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5294,7 +5299,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5337,7 +5342,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5351,10 +5356,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46002</v>
+        <v>44944</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5367,7 +5372,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5410,7 +5415,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5424,10 +5429,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45786</v>
+        <v>44979</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5439,13 +5444,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45642</v>
+        <v>45401</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5561,7 +5561,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45719</v>
+        <v>45561</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45820</v>
+        <v>44991</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.8</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5717,14 +5717,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45249</v>
+        <v>44984</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5780,7 +5780,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46146</v>
+        <v>45610</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5853,7 +5853,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45757</v>
+        <v>45249</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.7</v>
+        <v>6.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5940,10 +5940,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45754</v>
+        <v>46112</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5999,7 +5999,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6009,14 +6009,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45203</v>
+        <v>45754</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45229</v>
+        <v>46125</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6162,7 +6162,7 @@
         <v>45229</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45580</v>
+        <v>45799</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6291,7 +6291,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45965</v>
+        <v>45754</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45527</v>
+        <v>45166</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45338</v>
+        <v>45786</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6466,8 +6466,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6510,7 +6515,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6524,10 +6529,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44965</v>
+        <v>45239</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6540,7 +6545,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6583,7 +6588,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6597,10 +6602,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45525</v>
+        <v>45642</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6613,7 +6618,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6656,7 +6661,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6670,10 +6675,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45527</v>
+        <v>45280</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6686,7 +6691,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6729,7 +6734,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6743,10 +6748,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44502</v>
+        <v>46000</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6758,13 +6763,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45021</v>
+        <v>45527</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46195</v>
+        <v>45324</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45194</v>
+        <v>46146</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45619</v>
+        <v>44965</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45775</v>
+        <v>45558</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7182,14 +7182,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45932</v>
+        <v>45063</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45561</v>
+        <v>45194</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46273</v>
+        <v>45519</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46281</v>
+        <v>45775</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46281</v>
+        <v>44845</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7537,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46282</v>
+        <v>45965</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7610,7 +7610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7620,14 +7620,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46281</v>
+        <v>45034</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46281</v>
+        <v>44515</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45166</v>
+        <v>44922</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7829,7 +7829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46286</v>
+        <v>44574</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7902,7 +7902,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7916,10 +7916,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44805</v>
+        <v>46195</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7985,14 +7985,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44953</v>
+        <v>45253</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8048,7 +8048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8058,14 +8058,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44953</v>
+        <v>45580</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8121,7 +8121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45191</v>
+        <v>45757</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8204,14 +8204,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44755</v>
+        <v>45049</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8277,14 +8277,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45591</v>
+        <v>45203</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8350,14 +8350,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44602</v>
+        <v>45932</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8413,7 +8413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45107</v>
+        <v>44602</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46058</v>
+        <v>45251</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8573,10 +8573,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44922</v>
+        <v>44755</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8642,14 +8642,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45049</v>
+        <v>45591</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8715,14 +8715,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44922</v>
+        <v>45619</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8788,14 +8788,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44929</v>
+        <v>45719</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8861,14 +8861,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44991</v>
+        <v>44953</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45394</v>
+        <v>44953</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45324</v>
+        <v>46273</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9080,14 +9080,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44984</v>
+        <v>45229</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9157,10 +9157,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44845</v>
+        <v>46281</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45251</v>
+        <v>45177</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45253</v>
+        <v>46281</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44979</v>
+        <v>46281</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45617</v>
+        <v>46281</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9525,7 +9525,7 @@
         <v>45680</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45789</v>
+        <v>45617</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45709</v>
+        <v>46282</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45666</v>
+        <v>46286</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9800,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45579</v>
+        <v>46058</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9873,7 +9873,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9887,10 +9887,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9946,7 +9946,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 417-2023</t>
+          <t>A 2764-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44929</v>
+        <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Ask
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 417-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Nattskärra
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 2764-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45825</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44944</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44715</v>
+        <v>44515</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44922</v>
+        <v>45401</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45107</v>
+        <v>45229</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45191</v>
+        <v>44901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45021</v>
+        <v>45709</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44900</v>
+        <v>45666</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44986</v>
+        <v>45579</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3390,13 +3390,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3439,7 +3434,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3453,10 +3448,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46002</v>
+        <v>45720</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3469,7 +3464,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3512,7 +3507,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3526,10 +3521,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45666</v>
+        <v>45239</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3542,7 +3537,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3585,7 +3580,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3599,10 +3594,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45789</v>
+        <v>44944</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3615,7 +3610,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3658,7 +3653,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3672,10 +3667,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45579</v>
+        <v>44922</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3688,7 +3683,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3731,7 +3726,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3745,10 +3740,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45709</v>
+        <v>45642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3761,7 +3756,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3804,7 +3799,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3814,14 +3809,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44960</v>
+        <v>45898</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3834,7 +3829,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3877,7 +3872,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3894,7 +3889,7 @@
         <v>44929</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3907,7 +3902,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3950,7 +3945,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3964,10 +3959,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44929</v>
+        <v>45203</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3980,7 +3975,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4023,7 +4018,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4037,10 +4032,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45720</v>
+        <v>45519</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4053,7 +4048,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4096,7 +4091,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4110,10 +4105,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45642</v>
+        <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4126,7 +4121,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4169,7 +4164,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4179,14 +4174,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45898</v>
+        <v>45820</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4199,7 +4194,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4242,7 +4237,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4252,14 +4247,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44929</v>
+        <v>44574</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4272,7 +4267,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4315,7 +4310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4325,14 +4320,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44930</v>
+        <v>45558</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4345,7 +4340,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4388,7 +4383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44805</v>
+        <v>44922</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4418,7 +4413,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4461,7 +4456,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4475,10 +4470,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45820</v>
+        <v>44986</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4490,8 +4485,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>7.8</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44922</v>
+        <v>45525</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45525</v>
+        <v>45960</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4690,14 +4690,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45394</v>
+        <v>44960</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4763,14 +4763,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45960</v>
+        <v>45034</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45229</v>
+        <v>44900</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4899,7 +4899,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45338</v>
+        <v>44715</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4972,7 +4972,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45527</v>
+        <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5045,7 +5045,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44901</v>
+        <v>45177</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5128,14 +5128,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44922</v>
+        <v>44930</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5191,7 +5191,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5201,14 +5201,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44502</v>
+        <v>44929</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5220,13 +5220,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5269,7 +5264,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5279,14 +5274,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45203</v>
+        <v>46002</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5299,7 +5294,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5342,7 +5337,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5356,10 +5351,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44944</v>
+        <v>45719</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5372,7 +5367,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5415,7 +5410,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5429,10 +5424,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44979</v>
+        <v>45249</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5445,7 +5440,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5488,7 +5483,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5502,10 +5497,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45401</v>
+        <v>46112</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5518,7 +5513,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5561,7 +5556,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5575,10 +5570,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45561</v>
+        <v>46125</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5591,7 +5586,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5634,7 +5629,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5648,10 +5643,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44991</v>
+        <v>45757</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5664,7 +5659,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5707,7 +5702,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5717,14 +5712,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44984</v>
+        <v>45754</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5737,7 +5732,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5780,7 +5775,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5790,14 +5785,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45610</v>
+        <v>45203</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5810,7 +5805,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5853,7 +5848,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5867,10 +5862,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45249</v>
+        <v>45229</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5883,7 +5878,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5926,7 +5921,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5940,10 +5935,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46112</v>
+        <v>45229</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5956,7 +5951,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5999,7 +5994,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6013,10 +6008,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45754</v>
+        <v>45580</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6029,7 +6024,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6072,7 +6067,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6086,10 +6081,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46125</v>
+        <v>45754</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6102,7 +6097,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6145,7 +6140,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6159,10 +6154,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45229</v>
+        <v>46000</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6175,7 +6170,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6235,7 +6230,7 @@
         <v>45799</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6291,7 +6286,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6305,10 +6300,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45754</v>
+        <v>45527</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6321,7 +6316,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6364,7 +6359,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6378,10 +6373,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45166</v>
+        <v>45280</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6394,7 +6389,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6437,7 +6432,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6451,10 +6446,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45786</v>
+        <v>45338</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6466,13 +6461,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6515,7 +6505,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6529,10 +6519,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45239</v>
+        <v>44965</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6545,7 +6535,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6588,7 +6578,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6602,10 +6592,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45642</v>
+        <v>45527</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6618,7 +6608,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6661,7 +6651,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6675,10 +6665,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45280</v>
+        <v>44502</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6690,8 +6680,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6734,7 +6729,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6748,10 +6743,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46000</v>
+        <v>45786</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6763,8 +6758,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45527</v>
+        <v>45642</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6890,14 +6890,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45324</v>
+        <v>45021</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6970,7 +6970,7 @@
         <v>46146</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44965</v>
+        <v>45194</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7109,14 +7109,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45558</v>
+        <v>45619</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45063</v>
+        <v>45965</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45194</v>
+        <v>45775</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45519</v>
+        <v>45561</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45775</v>
+        <v>46195</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44845</v>
+        <v>45166</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7537,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45965</v>
+        <v>44805</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7610,7 +7610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45034</v>
+        <v>44953</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7683,7 +7683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7693,14 +7693,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44515</v>
+        <v>44953</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44922</v>
+        <v>45191</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7829,7 +7829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44574</v>
+        <v>44755</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7902,7 +7902,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7916,10 +7916,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46195</v>
+        <v>45591</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45253</v>
+        <v>44602</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8048,7 +8048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8062,10 +8062,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45580</v>
+        <v>45107</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8121,7 +8121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45757</v>
+        <v>44922</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45049</v>
+        <v>45932</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45203</v>
+        <v>45049</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8350,14 +8350,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45932</v>
+        <v>44922</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8413,7 +8413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8423,14 +8423,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44602</v>
+        <v>44929</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45251</v>
+        <v>44991</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8573,10 +8573,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44755</v>
+        <v>46273</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8642,14 +8642,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45591</v>
+        <v>45394</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8715,14 +8715,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45619</v>
+        <v>45324</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8788,14 +8788,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45719</v>
+        <v>44984</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8861,14 +8861,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44953</v>
+        <v>44845</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8934,14 +8934,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44953</v>
+        <v>46281</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45229</v>
+        <v>46282</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9160,7 +9160,7 @@
         <v>46281</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45177</v>
+        <v>46281</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46281</v>
+        <v>45251</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46281</v>
+        <v>45253</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45680</v>
+        <v>44979</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9598,7 +9598,7 @@
         <v>45617</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46282</v>
+        <v>46058</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46286</v>
+        <v>45680</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9800,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46058</v>
+        <v>45789</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9873,7 +9873,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9887,10 +9887,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9946,7 +9946,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE125"/>
+  <dimension ref="A1:AE126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 2764-2023</t>
+          <t>A 417-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44944</v>
+        <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,259 +871,259 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 29724-2022</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44755</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29724-2022 artfynd.xlsx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29724-2022 karta.png", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29724-2022 georefererad karta.tif", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 29724-2022 karta knärot.png", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29724-2022 FSC-klagomål.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29724-2022 FSC-klagomål mail.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29724-2022 tillsynsbegäran.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29724-2022 tillsynsbegäran mail.docx", "A 29724-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 2764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>Ask
 Vårstarr</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 417-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 29724-2022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44755</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>7</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Flagellkvastmossa</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29724-2022 artfynd.xlsx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29724-2022 karta.png", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29724-2022 georefererad karta.tif", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 29724-2022 karta knärot.png", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29724-2022 FSC-klagomål.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29724-2022 FSC-klagomål mail.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29724-2022 tillsynsbegäran.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29724-2022 tillsynsbegäran mail.docx", "A 29724-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45825</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 56101-2025</t>
+          <t>A 2763-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45973</v>
+        <v>44944</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1412,143 +1412,143 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 56101-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>Hasselticka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 2763-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 64871-2021</t>
+          <t>A 23080-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44512</v>
+        <v>44715</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23080-2022</t>
+          <t>A 65112-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44715</v>
+        <v>44515</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 65112-2021</t>
+          <t>A 36404-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44515</v>
+        <v>44804</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2346,6 +2346,11 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2392,7 +2397,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 36404-2022</t>
+          <t>A 1882-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2406,10 +2411,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44804</v>
+        <v>44574</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2421,13 +2426,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1882-2022</t>
+          <t>A 64871-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44574</v>
+        <v>44512</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 495-2022</t>
+          <t>A 65095-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44566</v>
+        <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2645,13 +2645,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2694,7 +2689,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 496-2022</t>
+          <t>A 61986-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2708,10 +2703,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44566</v>
+        <v>44502</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2725,11 +2720,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2767,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 65095-2021</t>
+          <t>A 495-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2781,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44515</v>
+        <v>44566</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2801,8 +2796,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61986-2021</t>
+          <t>A 496-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44502</v>
+        <v>44566</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2876,11 +2876,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44515</v>
+        <v>45229</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45401</v>
+        <v>44715</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45229</v>
+        <v>44922</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44901</v>
+        <v>44602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45709</v>
+        <v>45251</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45666</v>
+        <v>45338</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45579</v>
+        <v>44755</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3434,7 +3434,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45720</v>
+        <v>45527</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45239</v>
+        <v>44901</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44944</v>
+        <v>44965</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3653,7 +3653,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44922</v>
+        <v>45107</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3726,7 +3726,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45642</v>
+        <v>45558</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3809,14 +3809,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45898</v>
+        <v>45591</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3882,14 +3882,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44929</v>
+        <v>45191</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3955,14 +3955,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45203</v>
+        <v>45063</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45519</v>
+        <v>44922</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45063</v>
+        <v>45619</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45820</v>
+        <v>44502</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4193,8 +4193,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4237,7 +4242,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4247,14 +4252,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44574</v>
+        <v>45203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4267,7 +4272,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4310,7 +4315,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4324,10 +4329,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45558</v>
+        <v>44944</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4340,7 +4345,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4383,7 +4388,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44922</v>
+        <v>45194</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4413,7 +4418,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4456,7 +4461,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4470,10 +4475,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44986</v>
+        <v>45519</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4485,13 +4490,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45525</v>
+        <v>45719</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45960</v>
+        <v>45775</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44960</v>
+        <v>44900</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4763,14 +4763,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45034</v>
+        <v>44986</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4782,8 +4782,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4826,7 +4831,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4836,14 +4841,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44900</v>
+        <v>44953</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4856,7 +4861,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4899,7 +4904,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4909,14 +4914,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44715</v>
+        <v>44953</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4929,7 +4934,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4972,7 +4977,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4986,10 +4991,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45610</v>
+        <v>44845</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5002,7 +5007,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5045,7 +5050,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5055,14 +5060,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45177</v>
+        <v>45021</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5075,7 +5080,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5118,7 +5123,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5128,14 +5133,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44930</v>
+        <v>44979</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5148,7 +5153,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5191,7 +5196,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5205,10 +5210,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44929</v>
+        <v>45034</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5221,7 +5226,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5264,7 +5269,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5278,10 +5283,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46002</v>
+        <v>45229</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5294,7 +5299,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5337,7 +5342,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5351,10 +5356,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45719</v>
+        <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5367,7 +5372,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5410,7 +5415,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5424,10 +5429,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45249</v>
+        <v>45401</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5440,7 +5445,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5483,7 +5488,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5497,10 +5502,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46112</v>
+        <v>44922</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5513,7 +5518,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5556,7 +5561,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5570,10 +5575,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46125</v>
+        <v>45561</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5586,7 +5591,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5629,7 +5634,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5643,10 +5648,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45757</v>
+        <v>45177</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5659,7 +5664,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5702,7 +5707,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5716,10 +5721,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45754</v>
+        <v>44574</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5732,7 +5737,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5775,7 +5780,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5785,14 +5790,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45203</v>
+        <v>44960</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5805,7 +5810,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>6.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5848,7 +5853,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5862,10 +5867,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45229</v>
+        <v>45680</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5878,7 +5883,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5921,7 +5926,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5935,10 +5940,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45229</v>
+        <v>45617</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5951,7 +5956,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5994,7 +5999,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6008,10 +6013,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45580</v>
+        <v>44991</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6024,7 +6029,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6067,7 +6072,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6077,14 +6082,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45754</v>
+        <v>44984</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6097,7 +6102,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6140,7 +6145,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6154,10 +6159,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46000</v>
+        <v>45610</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6170,7 +6175,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6213,7 +6218,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6227,10 +6232,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45799</v>
+        <v>45666</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6243,7 +6248,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6286,7 +6291,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6300,10 +6305,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45527</v>
+        <v>45789</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6316,7 +6321,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6359,7 +6364,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6373,10 +6378,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45280</v>
+        <v>45249</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6389,7 +6394,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6432,7 +6437,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6446,10 +6451,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45338</v>
+        <v>45579</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6462,7 +6467,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6505,7 +6510,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6519,10 +6524,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44965</v>
+        <v>45709</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6535,7 +6540,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6578,7 +6583,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6588,14 +6593,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45527</v>
+        <v>44929</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6608,7 +6613,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6651,7 +6656,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6661,14 +6666,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44502</v>
+        <v>44929</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6680,13 +6685,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45786</v>
+        <v>45754</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6758,13 +6758,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6802,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6821,10 +6816,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45642</v>
+        <v>45720</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6837,7 +6832,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6880,7 +6875,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6890,14 +6885,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45021</v>
+        <v>45253</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6910,7 +6905,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6953,7 +6948,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6967,10 +6962,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46146</v>
+        <v>45580</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6983,7 +6978,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7021,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7036,14 +7031,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45194</v>
+        <v>44929</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7051,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7094,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7113,10 +7108,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45619</v>
+        <v>44930</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7129,7 +7124,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7172,7 +7167,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7186,10 +7181,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45965</v>
+        <v>45757</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7202,7 +7197,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7245,7 +7240,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7259,10 +7254,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45775</v>
+        <v>44805</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7270,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7313,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7328,14 +7323,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45561</v>
+        <v>45049</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7348,7 +7343,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7386,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7405,10 +7400,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46195</v>
+        <v>45229</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7421,7 +7416,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7481,7 +7476,7 @@
         <v>45166</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7537,7 +7532,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7551,10 +7546,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44805</v>
+        <v>45820</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7567,7 +7562,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>7.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7610,7 +7605,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7620,14 +7615,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44953</v>
+        <v>45239</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7640,7 +7635,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7683,7 +7678,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7697,10 +7692,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44953</v>
+        <v>45203</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7713,7 +7708,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7756,7 +7751,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7770,10 +7765,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45191</v>
+        <v>44922</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7786,7 +7781,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7829,7 +7824,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7843,10 +7838,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44755</v>
+        <v>45527</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7859,7 +7854,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7902,7 +7897,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7916,10 +7911,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45591</v>
+        <v>45525</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7932,7 +7927,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7975,7 +7970,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7989,10 +7984,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44602</v>
+        <v>45324</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8005,7 +8000,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8048,7 +8043,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8058,14 +8053,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45107</v>
+        <v>45394</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8078,7 +8073,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8121,7 +8116,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8135,10 +8130,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44922</v>
+        <v>45642</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8151,7 +8146,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8194,7 +8189,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8208,10 +8203,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45932</v>
+        <v>45898</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8224,7 +8219,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8267,7 +8262,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8277,14 +8272,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45049</v>
+        <v>45960</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8297,7 +8292,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8340,7 +8335,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8354,10 +8349,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44922</v>
+        <v>46002</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8370,7 +8365,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8413,7 +8408,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8423,14 +8418,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44929</v>
+        <v>46112</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8443,7 +8438,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8486,7 +8481,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8500,10 +8495,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44991</v>
+        <v>46125</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8516,7 +8511,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8559,7 +8554,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8573,10 +8568,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46273</v>
+        <v>45799</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8589,7 +8584,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8632,7 +8627,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8642,14 +8637,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45394</v>
+        <v>45754</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8662,7 +8657,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8700,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8719,10 +8714,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45324</v>
+        <v>45786</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8734,8 +8729,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8788,14 +8788,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44984</v>
+        <v>45642</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44845</v>
+        <v>45280</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46281</v>
+        <v>46000</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46281</v>
+        <v>46146</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46282</v>
+        <v>45965</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9157,10 +9157,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46281</v>
+        <v>46195</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9226,14 +9226,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46281</v>
+        <v>45932</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46286</v>
+        <v>46273</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45251</v>
+        <v>46281</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45253</v>
+        <v>46281</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44979</v>
+        <v>46281</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45617</v>
+        <v>46281</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46058</v>
+        <v>46282</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45680</v>
+        <v>46286</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9800,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45789</v>
+        <v>46058</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9873,24 +9873,24 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>A 40535-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44715</v>
+        <v>46295</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="V124" s="2" t="inlineStr"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
           <t>S 3719-2023</t>
@@ -9963,7 +9963,7 @@
         <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10015,6 +10015,79 @@
         <v>0</v>
       </c>
       <c r="V125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>S 3071-2022</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>44715</v>
+      </c>
+      <c r="E126" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 417-2023</t>
+          <t>A 2764-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44929</v>
+        <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,259 +871,259 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Ask
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 417-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Nattskärra
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>A 29724-2022</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>44755</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="E6" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>11.8</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>2</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>7</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Flagellkvastmossa</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29724-2022 artfynd.xlsx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29724-2022 karta.png", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29724-2022 georefererad karta.tif", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/knärot/A 29724-2022 karta knärot.png", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29724-2022 FSC-klagomål.docx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29724-2022 FSC-klagomål mail.docx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29724-2022 tillsynsbegäran.docx", "A 29724-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29724-2022 tillsynsbegäran mail.docx", "A 29724-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 2764-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 29819-2025</t>
+          <t>A 56101-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45825</v>
+        <v>45973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1299,361 +1299,361 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 29819-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45825</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Nattskärra</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31382-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 2763-2023</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>44944</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>2.5</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 56101-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31382-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 23080-2022</t>
+          <t>A 64871-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44715</v>
+        <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 65112-2021</t>
+          <t>A 23080-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44515</v>
+        <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 36404-2022</t>
+          <t>A 65112-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44804</v>
+        <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2346,11 +2346,6 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2397,7 +2392,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 1882-2022</t>
+          <t>A 36404-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2411,10 +2406,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44574</v>
+        <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2426,8 +2421,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 64871-2021</t>
+          <t>A 1882-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44512</v>
+        <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 65095-2021</t>
+          <t>A 495-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44515</v>
+        <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2645,8 +2645,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2689,7 +2694,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61986-2021</t>
+          <t>A 496-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2703,10 +2708,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44502</v>
+        <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2720,11 +2725,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2767,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 495-2022</t>
+          <t>A 65095-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2781,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44566</v>
+        <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2796,13 +2801,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 496-2022</t>
+          <t>A 61986-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44566</v>
+        <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2876,11 +2876,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2940,7 +2940,7 @@
         <v>45229</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44715</v>
+        <v>44515</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44922</v>
+        <v>45401</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44602</v>
+        <v>44901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45251</v>
+        <v>45709</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45338</v>
+        <v>45666</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44755</v>
+        <v>45579</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3434,7 +3434,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45527</v>
+        <v>45720</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44901</v>
+        <v>45239</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44965</v>
+        <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3653,7 +3653,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45107</v>
+        <v>44944</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3726,7 +3726,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45558</v>
+        <v>44922</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3809,14 +3809,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45591</v>
+        <v>45898</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3882,14 +3882,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45191</v>
+        <v>44929</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3955,14 +3955,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45063</v>
+        <v>45203</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44922</v>
+        <v>45519</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45619</v>
+        <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44502</v>
+        <v>44574</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4193,13 +4193,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4242,7 +4237,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4252,14 +4247,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45203</v>
+        <v>45558</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4272,7 +4267,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4315,7 +4310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4329,10 +4324,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44944</v>
+        <v>44922</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4345,7 +4340,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4388,7 +4383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45194</v>
+        <v>44986</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4417,8 +4412,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45519</v>
+        <v>45960</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45719</v>
+        <v>46112</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45775</v>
+        <v>46125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44900</v>
+        <v>44960</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4763,14 +4763,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44986</v>
+        <v>45034</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4782,13 +4782,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4831,7 +4826,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4841,14 +4836,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44953</v>
+        <v>45754</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4861,7 +4856,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4904,7 +4899,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4914,14 +4909,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44953</v>
+        <v>44900</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4934,7 +4929,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4977,7 +4972,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4991,10 +4986,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44845</v>
+        <v>45820</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5007,7 +5002,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.9</v>
+        <v>7.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5050,7 +5045,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5060,14 +5055,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45021</v>
+        <v>46000</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5080,7 +5075,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5123,7 +5118,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5137,10 +5132,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44979</v>
+        <v>45799</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5153,7 +5148,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5196,7 +5191,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5206,14 +5201,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45034</v>
+        <v>44715</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5226,7 +5221,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5269,7 +5264,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5283,10 +5278,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45229</v>
+        <v>45610</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5299,7 +5294,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5342,7 +5337,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5356,10 +5351,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44515</v>
+        <v>45280</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5372,7 +5367,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5415,7 +5410,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5429,10 +5424,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45401</v>
+        <v>45177</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5445,7 +5440,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5488,7 +5483,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5502,10 +5497,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44922</v>
+        <v>46002</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5518,7 +5513,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5561,7 +5556,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5571,14 +5566,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45561</v>
+        <v>44930</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5591,7 +5586,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5634,7 +5629,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5644,14 +5639,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45177</v>
+        <v>44929</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5664,7 +5659,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5707,7 +5702,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5721,10 +5716,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44574</v>
+        <v>45786</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5736,8 +5731,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5780,7 +5780,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44960</v>
+        <v>45642</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5853,7 +5853,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45680</v>
+        <v>45719</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5940,10 +5940,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45617</v>
+        <v>45525</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5999,7 +5999,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6013,10 +6013,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44991</v>
+        <v>45249</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>6.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6082,14 +6082,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44984</v>
+        <v>45757</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6145,7 +6145,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45610</v>
+        <v>46146</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6218,7 +6218,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45666</v>
+        <v>45754</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6291,7 +6291,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6301,14 +6301,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45789</v>
+        <v>45203</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45249</v>
+        <v>45229</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45579</v>
+        <v>45229</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6510,7 +6510,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45709</v>
+        <v>45580</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6583,7 +6583,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6593,14 +6593,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44929</v>
+        <v>45527</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6656,7 +6656,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6666,14 +6666,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44929</v>
+        <v>45338</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6729,7 +6729,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45754</v>
+        <v>44965</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6802,7 +6802,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6816,10 +6816,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45720</v>
+        <v>45965</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45253</v>
+        <v>45527</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45580</v>
+        <v>44502</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6977,8 +6977,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7021,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7035,10 +7040,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44929</v>
+        <v>45021</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7051,7 +7056,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7094,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7104,14 +7109,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44930</v>
+        <v>45194</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7124,7 +7129,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7167,7 +7172,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7181,10 +7186,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45757</v>
+        <v>46195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7197,7 +7202,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7240,7 +7245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7250,14 +7255,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44805</v>
+        <v>45619</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7270,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7313,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7323,14 +7328,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45049</v>
+        <v>45775</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7343,7 +7348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7386,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7400,10 +7405,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45229</v>
+        <v>45561</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7416,7 +7421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7459,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7469,14 +7474,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45166</v>
+        <v>45932</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7489,7 +7494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7532,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7546,10 +7551,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45820</v>
+        <v>46273</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7562,7 +7567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7605,7 +7610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7619,10 +7624,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45239</v>
+        <v>45166</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7635,7 +7640,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7678,7 +7683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7688,14 +7693,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45203</v>
+        <v>44805</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7708,7 +7713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7751,7 +7756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7761,14 +7766,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44922</v>
+        <v>44953</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7781,7 +7786,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7824,7 +7829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7834,14 +7839,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45527</v>
+        <v>44953</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7854,7 +7859,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7897,7 +7902,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7911,10 +7916,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45525</v>
+        <v>45191</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7927,7 +7932,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7970,7 +7975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7984,10 +7989,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45324</v>
+        <v>44755</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8000,7 +8005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8043,7 +8048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8053,14 +8058,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45394</v>
+        <v>45591</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8073,7 +8078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8116,7 +8121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8130,10 +8135,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45642</v>
+        <v>46281</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8146,7 +8151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8189,7 +8194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8199,14 +8204,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45898</v>
+        <v>46281</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8219,7 +8224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8262,7 +8267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8276,10 +8281,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45960</v>
+        <v>44602</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8292,7 +8297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8335,7 +8340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8349,10 +8354,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46002</v>
+        <v>45107</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8365,7 +8370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8408,7 +8413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8422,10 +8427,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46112</v>
+        <v>46282</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8438,7 +8443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8481,7 +8486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8495,10 +8500,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46125</v>
+        <v>46281</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8511,7 +8516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8554,7 +8559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8568,10 +8573,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45799</v>
+        <v>46281</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8584,7 +8589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8627,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8641,10 +8646,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45754</v>
+        <v>46286</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8657,7 +8662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8700,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8714,10 +8719,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45786</v>
+        <v>44922</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8729,13 +8734,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8788,14 +8788,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45642</v>
+        <v>45049</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45280</v>
+        <v>44922</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8934,14 +8934,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46000</v>
+        <v>44929</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46146</v>
+        <v>44991</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45965</v>
+        <v>46058</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9153,14 +9153,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46195</v>
+        <v>45394</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9226,14 +9226,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45932</v>
+        <v>45324</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9299,14 +9299,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46273</v>
+        <v>44984</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46281</v>
+        <v>44845</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 40535-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46281</v>
+        <v>45251</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46281</v>
+        <v>45253</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46282</v>
+        <v>44979</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46286</v>
+        <v>45617</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9800,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46058</v>
+        <v>45680</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9873,7 +9873,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 40535-2026</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9887,10 +9887,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46295</v>
+        <v>45789</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9946,7 +9946,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10019,7 +10019,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10033,10 +10033,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 2764-2023</t>
+          <t>A 417-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44944</v>
+        <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2764-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Ask
 Vårstarr</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 417-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>45825</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31382-2026</t>
+          <t>A 2763-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46219</v>
+        <v>44944</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1517,143 +1517,143 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31382-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 2763-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45229</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44515</v>
+        <v>45107</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45401</v>
+        <v>44715</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44901</v>
+        <v>45191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45709</v>
+        <v>45021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45666</v>
+        <v>44986</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3317,8 +3317,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3366,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3380,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45579</v>
+        <v>44900</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3391,7 +3396,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3434,7 +3439,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3448,10 +3453,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45720</v>
+        <v>46002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3464,7 +3469,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3507,7 +3512,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3521,10 +3526,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45239</v>
+        <v>44960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3537,7 +3542,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3580,7 +3585,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3594,10 +3599,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45642</v>
+        <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3610,7 +3615,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3653,7 +3658,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3667,10 +3672,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44944</v>
+        <v>45789</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3683,7 +3688,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3726,7 +3731,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3736,14 +3741,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44922</v>
+        <v>44929</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3756,7 +3761,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3799,7 +3804,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3813,10 +3818,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45898</v>
+        <v>44929</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3872,7 +3877,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3882,14 +3887,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44929</v>
+        <v>45579</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3902,7 +3907,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3945,7 +3950,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3955,14 +3960,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45203</v>
+        <v>45709</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3975,7 +3980,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4018,7 +4023,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4032,10 +4037,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45519</v>
+        <v>45642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4048,7 +4053,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4091,7 +4096,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4101,14 +4106,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45063</v>
+        <v>44929</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4164,7 +4169,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4174,14 +4179,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44574</v>
+        <v>44930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4194,7 +4199,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4237,7 +4242,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4247,14 +4252,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45558</v>
+        <v>45898</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4267,7 +4272,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4310,7 +4315,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4324,10 +4329,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44922</v>
+        <v>44805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4340,7 +4345,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4383,7 +4388,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44986</v>
+        <v>45720</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4412,13 +4417,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45960</v>
+        <v>44922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4544,14 +4544,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46112</v>
+        <v>45394</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46125</v>
+        <v>45229</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44960</v>
+        <v>45338</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4763,14 +4763,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45034</v>
+        <v>45960</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45754</v>
+        <v>45527</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4899,7 +4899,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44900</v>
+        <v>44901</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4972,7 +4972,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45820</v>
+        <v>44922</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.8</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5045,7 +5045,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46000</v>
+        <v>44502</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5074,8 +5074,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5118,7 +5123,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5128,14 +5133,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45799</v>
+        <v>45203</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5148,7 +5153,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5191,7 +5196,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5205,10 +5210,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44715</v>
+        <v>44944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5221,7 +5226,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5264,7 +5269,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5278,10 +5283,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45610</v>
+        <v>46112</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5294,7 +5299,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5337,7 +5342,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5351,10 +5356,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45280</v>
+        <v>45820</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5367,7 +5372,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5410,7 +5415,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5424,10 +5429,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45177</v>
+        <v>46125</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5440,7 +5445,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5483,7 +5488,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5497,10 +5502,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46002</v>
+        <v>44979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5513,7 +5518,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5556,7 +5561,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5566,14 +5571,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44930</v>
+        <v>45401</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5586,7 +5591,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5629,7 +5634,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5639,14 +5644,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44929</v>
+        <v>45799</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5659,7 +5664,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5702,7 +5707,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5716,10 +5721,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45786</v>
+        <v>45754</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5731,13 +5736,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5780,7 +5780,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45642</v>
+        <v>45561</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5853,7 +5853,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45719</v>
+        <v>45786</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5882,8 +5882,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5926,7 +5931,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5940,10 +5945,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45525</v>
+        <v>45642</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5956,7 +5961,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5999,7 +6004,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6013,10 +6018,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45249</v>
+        <v>45280</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6029,7 +6034,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6072,7 +6077,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6086,10 +6091,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45757</v>
+        <v>44991</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6102,7 +6107,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6145,7 +6150,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6155,14 +6160,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46146</v>
+        <v>44984</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6175,7 +6180,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6218,7 +6223,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6232,10 +6237,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45754</v>
+        <v>45610</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6248,7 +6253,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6291,7 +6296,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6301,14 +6306,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45203</v>
+        <v>45249</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6321,7 +6326,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.3</v>
+        <v>6.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6364,7 +6369,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6378,10 +6383,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45229</v>
+        <v>46000</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6394,7 +6399,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6437,7 +6442,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6451,10 +6456,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45229</v>
+        <v>45754</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6467,7 +6472,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6510,7 +6515,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6524,10 +6529,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45580</v>
+        <v>45525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6540,7 +6545,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6583,7 +6588,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6597,10 +6602,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45527</v>
+        <v>46146</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6613,7 +6618,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6656,7 +6661,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6670,10 +6675,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45338</v>
+        <v>45229</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6686,7 +6691,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6729,7 +6734,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6743,10 +6748,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44965</v>
+        <v>45166</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6802,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6816,10 +6821,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45965</v>
+        <v>45239</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6832,7 +6837,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6875,7 +6880,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6889,10 +6894,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45527</v>
+        <v>45965</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6905,7 +6910,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6948,7 +6953,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6962,10 +6967,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44502</v>
+        <v>45527</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6977,13 +6982,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45021</v>
+        <v>45324</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45194</v>
+        <v>44965</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46195</v>
+        <v>45558</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7255,14 +7255,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45619</v>
+        <v>46195</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45775</v>
+        <v>45063</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45561</v>
+        <v>45194</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7474,14 +7474,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45932</v>
+        <v>45519</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7537,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46273</v>
+        <v>45775</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7610,7 +7610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45166</v>
+        <v>44845</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7683,7 +7683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7693,14 +7693,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44805</v>
+        <v>45034</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44953</v>
+        <v>45932</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7829,7 +7829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7839,14 +7839,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44953</v>
+        <v>44515</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7902,7 +7902,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7916,10 +7916,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45191</v>
+        <v>44922</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44755</v>
+        <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8048,7 +8048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8062,10 +8062,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45591</v>
+        <v>46273</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8121,7 +8121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8138,7 +8138,7 @@
         <v>46281</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8211,7 +8211,7 @@
         <v>46281</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44602</v>
+        <v>46281</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45107</v>
+        <v>46281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8430,7 +8430,7 @@
         <v>46282</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46281</v>
+        <v>45253</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8573,10 +8573,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46281</v>
+        <v>45580</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46286</v>
+        <v>45757</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44922</v>
+        <v>46286</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8795,7 +8795,7 @@
         <v>45049</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44922</v>
+        <v>46058</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 40535-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8934,14 +8934,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44929</v>
+        <v>46295</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9007,14 +9007,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44991</v>
+        <v>45203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46058</v>
+        <v>44602</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9153,14 +9153,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45394</v>
+        <v>45251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45324</v>
+        <v>44755</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9299,14 +9299,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44984</v>
+        <v>45591</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9372,14 +9372,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44845</v>
+        <v>45619</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 40535-2026</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46295</v>
+        <v>45719</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9518,14 +9518,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45251</v>
+        <v>44953</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9591,14 +9591,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45253</v>
+        <v>44953</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44979</v>
+        <v>45229</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45617</v>
+        <v>45177</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9817,7 +9817,7 @@
         <v>45680</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9887,10 +9887,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45789</v>
+        <v>45617</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9946,7 +9946,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10019,7 +10019,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10033,10 +10033,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>44944</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>45825</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44944</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45107</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>44715</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44986</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44900</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>45789</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44929</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44929</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45579</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45709</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44929</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45898</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45720</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>45394</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>45229</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45338</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45960</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45527</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44901</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44922</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44502</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45203</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46112</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>45820</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46125</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>44979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45401</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45799</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45754</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45561</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45786</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45642</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45280</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44991</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44984</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45610</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45249</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>46000</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45754</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>46146</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45229</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45166</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45239</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45965</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>45527</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>45324</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>44965</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45558</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>46195</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45063</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45194</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45519</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45775</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44845</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>45034</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45932</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44515</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>44922</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>46273</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>46281</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>46281</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>46281</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>46281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>46282</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45253</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45580</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45757</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>46286</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45049</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>46058</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>46295</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>45203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44602</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>45251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44755</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>45591</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>45619</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45719</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44953</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44953</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45229</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45177</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45680</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45617</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44715</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>44944</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>45825</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44944</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45107</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>44715</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44986</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44900</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44960</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>45789</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44929</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44929</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45579</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45709</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44929</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45898</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44805</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45720</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>45394</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>45229</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45338</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45960</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45527</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44901</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>44922</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44502</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45203</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44944</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46112</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>45820</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46125</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>44979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45401</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45799</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45754</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45561</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45786</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45642</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45280</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44991</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44984</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45610</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45249</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>46000</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45754</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45525</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>46146</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>45229</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45166</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45239</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45965</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>45527</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>45324</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>44965</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>45558</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>46195</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45063</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>45194</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45519</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45775</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44845</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>45034</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45932</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44515</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>44922</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44574</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>46273</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>46281</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>46281</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>46281</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>46281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>46282</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>45253</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45580</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45757</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>46286</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>45049</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>46058</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>46295</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>45203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44602</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>45251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44755</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>45591</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>45619</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45719</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44953</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44953</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>45229</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>45177</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45680</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45617</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44715</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 417-2023</t>
+          <t>A 2764-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44929</v>
+        <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Ask
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 417-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Nattskärra
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 2764-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 56101-2025</t>
+          <t>A 29819-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45973</v>
+        <v>45825</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1299,155 +1299,155 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 56101-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Hasselticka</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 29819-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45825</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2763-2023</t>
+          <t>A 31382-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44944</v>
+        <v>46219</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1517,143 +1517,143 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 2763-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31382-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>44515</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45107</v>
+        <v>45229</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44715</v>
+        <v>45401</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45191</v>
+        <v>44901</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45021</v>
+        <v>45239</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44986</v>
+        <v>44922</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3317,13 +3317,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3366,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3380,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44900</v>
+        <v>44944</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3396,7 +3391,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3439,7 +3434,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3449,14 +3444,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46002</v>
+        <v>44929</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3469,7 +3464,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3512,7 +3507,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3522,14 +3517,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44960</v>
+        <v>45203</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3542,7 +3537,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3585,7 +3580,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3599,10 +3594,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45666</v>
+        <v>45519</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3615,7 +3610,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3658,7 +3653,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3672,10 +3667,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45789</v>
+        <v>45063</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3688,7 +3683,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3731,7 +3726,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3741,14 +3736,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44929</v>
+        <v>45820</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3761,7 +3756,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>7.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3804,7 +3799,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3814,14 +3809,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44929</v>
+        <v>44574</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3834,7 +3829,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3877,7 +3872,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3891,10 +3886,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45579</v>
+        <v>45558</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3907,7 +3902,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3950,7 +3945,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3964,10 +3959,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45709</v>
+        <v>45642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3980,7 +3975,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4023,7 +4018,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4033,14 +4028,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45642</v>
+        <v>45898</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4053,7 +4048,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4096,7 +4091,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4106,14 +4101,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44929</v>
+        <v>44922</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4126,7 +4121,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4169,7 +4164,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4179,14 +4174,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44930</v>
+        <v>44986</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4198,8 +4193,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4252,14 +4252,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45898</v>
+        <v>45525</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44805</v>
+        <v>44960</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4398,14 +4398,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45720</v>
+        <v>45034</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44922</v>
+        <v>44900</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4544,14 +4544,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45394</v>
+        <v>44715</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45229</v>
+        <v>45610</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45338</v>
+        <v>45177</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4770,7 +4770,7 @@
         <v>45960</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45527</v>
+        <v>44930</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4899,7 +4899,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4909,14 +4909,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44901</v>
+        <v>44929</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4972,7 +4972,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44922</v>
+        <v>46112</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5045,7 +5045,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44502</v>
+        <v>45719</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5074,13 +5074,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5123,7 +5118,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5133,14 +5128,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45203</v>
+        <v>46125</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5196,7 +5191,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5210,10 +5205,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44944</v>
+        <v>45249</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5226,7 +5221,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5269,7 +5264,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5283,10 +5278,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46112</v>
+        <v>45757</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5299,7 +5294,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5342,7 +5337,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5356,10 +5351,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45820</v>
+        <v>46002</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5372,7 +5367,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5415,7 +5410,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5429,10 +5424,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46125</v>
+        <v>45754</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5445,7 +5440,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5488,7 +5483,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5498,14 +5493,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44979</v>
+        <v>45203</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5518,7 +5513,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5561,7 +5556,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5575,10 +5570,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45401</v>
+        <v>45229</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5591,7 +5586,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5634,7 +5629,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5648,10 +5643,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45799</v>
+        <v>45229</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5664,7 +5659,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5707,7 +5702,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5721,10 +5716,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45754</v>
+        <v>45580</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5780,7 +5775,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5794,10 +5789,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45561</v>
+        <v>45754</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5810,7 +5805,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5853,7 +5848,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5867,10 +5862,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45786</v>
+        <v>46000</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5882,13 +5877,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5931,7 +5921,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5945,10 +5935,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45642</v>
+        <v>45799</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5961,7 +5951,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6021,7 +6011,7 @@
         <v>45280</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6077,7 +6067,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6091,10 +6081,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44991</v>
+        <v>45527</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6107,7 +6097,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6150,7 +6140,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6160,14 +6150,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44984</v>
+        <v>45338</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6180,7 +6170,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6223,7 +6213,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6237,10 +6227,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45610</v>
+        <v>44965</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6296,7 +6286,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6310,10 +6300,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45249</v>
+        <v>45786</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6325,8 +6315,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>6.1</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6369,7 +6364,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6383,10 +6378,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46000</v>
+        <v>45642</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6399,7 +6394,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6442,7 +6437,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6456,10 +6451,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45754</v>
+        <v>45527</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6472,7 +6467,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6515,7 +6510,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6529,10 +6524,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45525</v>
+        <v>44502</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6544,8 +6539,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6605,7 +6605,7 @@
         <v>46146</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45229</v>
+        <v>45021</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45166</v>
+        <v>45965</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45239</v>
+        <v>45194</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6890,14 +6890,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45965</v>
+        <v>45619</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45527</v>
+        <v>45775</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45324</v>
+        <v>45561</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44965</v>
+        <v>46195</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45558</v>
+        <v>45166</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7255,14 +7255,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46195</v>
+        <v>45932</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45063</v>
+        <v>44805</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45194</v>
+        <v>44953</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7474,14 +7474,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45519</v>
+        <v>44953</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7537,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45775</v>
+        <v>45191</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7610,7 +7610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44845</v>
+        <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7683,7 +7683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7693,14 +7693,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45034</v>
+        <v>45591</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7766,14 +7766,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45932</v>
+        <v>44602</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7829,7 +7829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44515</v>
+        <v>45107</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7919,7 +7919,7 @@
         <v>44922</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44574</v>
+        <v>46273</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8048,7 +8048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8058,14 +8058,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46273</v>
+        <v>45049</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8121,7 +8121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46281</v>
+        <v>44922</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8204,14 +8204,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46281</v>
+        <v>44929</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46281</v>
+        <v>44991</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8357,7 +8357,7 @@
         <v>46281</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8413,7 +8413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45253</v>
+        <v>46282</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8573,10 +8573,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45580</v>
+        <v>46281</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45757</v>
+        <v>46281</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8715,14 +8715,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46286</v>
+        <v>45394</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8788,14 +8788,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45049</v>
+        <v>45324</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46058</v>
+        <v>46286</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 40535-2026</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8934,14 +8934,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46295</v>
+        <v>44984</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9007,14 +9007,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45203</v>
+        <v>44845</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44602</v>
+        <v>46058</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>45251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44755</v>
+        <v>45253</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45591</v>
+        <v>44979</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9372,14 +9372,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45619</v>
+        <v>45617</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 40535-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45719</v>
+        <v>46295</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9518,14 +9518,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44953</v>
+        <v>45680</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9591,14 +9591,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44953</v>
+        <v>45789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45229</v>
+        <v>45709</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45177</v>
+        <v>45666</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45680</v>
+        <v>45579</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9873,7 +9873,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9887,10 +9887,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45617</v>
+        <v>45720</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9946,7 +9946,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10019,7 +10019,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10033,10 +10033,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE126"/>
+  <dimension ref="A1:AE127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 2764-2023</t>
+          <t>A 417-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44944</v>
+        <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2764-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Ask
 Vårstarr</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 417-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45825</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 31382-2026</t>
+          <t>A 2763-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46219</v>
+        <v>44944</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1517,143 +1517,143 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 31382-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 2763-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10328-2022</t>
+          <t>A 6822-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44623</v>
+        <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 6822-2022</t>
+          <t>A 10328-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44602</v>
+        <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44515</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45229</v>
+        <v>44715</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45401</v>
+        <v>45191</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44901</v>
+        <v>45107</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45239</v>
+        <v>44900</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3298,14 +3298,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44922</v>
+        <v>45021</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44944</v>
+        <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3390,8 +3390,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3434,7 +3439,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3444,14 +3449,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44929</v>
+        <v>44960</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3464,7 +3469,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3507,7 +3512,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3521,10 +3526,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45203</v>
+        <v>44929</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3537,7 +3542,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3580,7 +3585,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3590,14 +3595,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45519</v>
+        <v>44929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3610,7 +3615,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3653,7 +3658,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3663,14 +3668,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45063</v>
+        <v>44929</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3726,7 +3731,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3736,14 +3741,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45820</v>
+        <v>44930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3756,7 +3761,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3799,7 +3804,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3813,10 +3818,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44574</v>
+        <v>44805</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3829,7 +3834,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3872,7 +3877,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3886,10 +3891,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45558</v>
+        <v>44922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3902,7 +3907,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3962,7 +3967,7 @@
         <v>45642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4035,7 +4040,7 @@
         <v>45898</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4091,7 +4096,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4101,14 +4106,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44922</v>
+        <v>45394</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4121,7 +4126,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4164,7 +4169,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4178,10 +4183,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44986</v>
+        <v>45229</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4193,13 +4198,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45525</v>
+        <v>45820</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>7.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44960</v>
+        <v>45338</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4398,14 +4398,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45034</v>
+        <v>45527</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44900</v>
+        <v>44901</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44715</v>
+        <v>44922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45610</v>
+        <v>44502</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4636,8 +4636,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4680,7 +4685,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4690,14 +4695,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45177</v>
+        <v>45203</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4710,7 +4715,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4753,7 +4758,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4767,10 +4772,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45960</v>
+        <v>44944</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4783,7 +4788,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4826,7 +4831,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4836,14 +4841,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44930</v>
+        <v>46112</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4856,7 +4861,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4899,7 +4904,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4909,14 +4914,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44929</v>
+        <v>45525</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4929,7 +4934,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4972,7 +4977,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4986,10 +4991,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46112</v>
+        <v>45960</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5002,7 +5007,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5045,7 +5050,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5059,10 +5064,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45719</v>
+        <v>46125</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5075,7 +5080,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5118,7 +5123,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5132,10 +5137,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46125</v>
+        <v>44979</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5191,7 +5196,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5205,10 +5210,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45249</v>
+        <v>45799</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5221,7 +5226,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5264,7 +5269,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5278,10 +5283,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45757</v>
+        <v>45754</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5294,7 +5299,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5337,7 +5342,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5351,10 +5356,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46002</v>
+        <v>45401</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5367,7 +5372,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5410,7 +5415,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5424,10 +5429,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45754</v>
+        <v>45786</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5439,8 +5444,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5483,7 +5493,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5493,14 +5503,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45203</v>
+        <v>45561</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5513,7 +5523,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.3</v>
+        <v>5.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5556,7 +5566,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5570,10 +5580,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5586,7 +5596,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5629,7 +5639,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5643,10 +5653,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45229</v>
+        <v>45280</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5659,7 +5669,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5702,7 +5712,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5716,10 +5726,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45580</v>
+        <v>46000</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5732,7 +5742,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5775,7 +5785,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5789,10 +5799,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45754</v>
+        <v>46002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5805,7 +5815,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5848,7 +5858,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5862,10 +5872,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46000</v>
+        <v>46146</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5878,7 +5888,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5921,7 +5931,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5935,10 +5945,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45799</v>
+        <v>45965</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5951,7 +5961,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5994,7 +6004,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6008,10 +6018,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45280</v>
+        <v>44991</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6024,7 +6034,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6067,7 +6077,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6077,14 +6087,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45527</v>
+        <v>44984</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6097,7 +6107,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6140,7 +6150,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6154,10 +6164,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45338</v>
+        <v>45610</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6170,7 +6180,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6213,7 +6223,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6227,10 +6237,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44965</v>
+        <v>45249</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6243,7 +6253,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6286,7 +6296,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6300,10 +6310,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45786</v>
+        <v>45754</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6315,13 +6325,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6364,7 +6369,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6378,10 +6383,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45642</v>
+        <v>46195</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6394,7 +6399,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6437,7 +6442,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6451,10 +6456,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45527</v>
+        <v>45229</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6467,7 +6472,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6510,7 +6515,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6524,10 +6529,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44502</v>
+        <v>45166</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6539,13 +6544,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46146</v>
+        <v>45239</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6661,7 +6661,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45021</v>
+        <v>45932</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45965</v>
+        <v>45527</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45194</v>
+        <v>45324</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6890,14 +6890,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45619</v>
+        <v>44965</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45775</v>
+        <v>45558</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45561</v>
+        <v>45063</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46195</v>
+        <v>45194</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45166</v>
+        <v>45519</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7255,14 +7255,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45932</v>
+        <v>46273</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44805</v>
+        <v>45775</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7401,14 +7401,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44953</v>
+        <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7474,14 +7474,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44953</v>
+        <v>46281</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7537,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7547,14 +7547,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45191</v>
+        <v>45034</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7610,7 +7610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44755</v>
+        <v>46281</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7683,7 +7683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45591</v>
+        <v>46281</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44602</v>
+        <v>46281</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7829,7 +7829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45107</v>
+        <v>44515</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7916,10 +7916,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44922</v>
+        <v>46282</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46273</v>
+        <v>44922</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8048,7 +8048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8058,14 +8058,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45049</v>
+        <v>46286</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8121,7 +8121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44922</v>
+        <v>44574</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8204,14 +8204,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44929</v>
+        <v>46058</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44991</v>
+        <v>45253</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46281</v>
+        <v>45580</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8413,7 +8413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46281</v>
+        <v>45757</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 40535-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46282</v>
+        <v>46295</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8569,14 +8569,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46281</v>
+        <v>45049</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 41576-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46281</v>
+        <v>46301</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45394</v>
+        <v>45203</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8792,10 +8792,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45324</v>
+        <v>44602</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46286</v>
+        <v>45251</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8934,14 +8934,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44984</v>
+        <v>44755</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44845</v>
+        <v>45591</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9080,14 +9080,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46058</v>
+        <v>45619</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9157,10 +9157,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45251</v>
+        <v>45719</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9226,14 +9226,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45253</v>
+        <v>44953</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9299,14 +9299,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44979</v>
+        <v>44953</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45617</v>
+        <v>45229</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 40535-2026</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46295</v>
+        <v>45177</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9525,7 +9525,7 @@
         <v>45680</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45789</v>
+        <v>45617</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45709</v>
+        <v>45666</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45666</v>
+        <v>45789</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9817,7 +9817,7 @@
         <v>45579</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9887,10 +9887,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45720</v>
+        <v>45709</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9946,24 +9946,24 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44715</v>
+        <v>45720</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="V125" s="2" t="inlineStr"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
           <t>S 3719-2023</t>
@@ -10036,7 +10036,7 @@
         <v>45222</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10088,6 +10088,79 @@
         <v>0</v>
       </c>
       <c r="V126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>S 3071-2022</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>44715</v>
+      </c>
+      <c r="E127" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE127"/>
+  <dimension ref="A1:AE129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 417-2023</t>
+          <t>A 2764-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44929</v>
+        <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Ask
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 417-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Nattskärra
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 2764-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45825</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44944</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 495-2022</t>
+          <t>A 65095-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44566</v>
+        <v>44515</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2645,13 +2645,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2694,7 +2689,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 496-2022</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2704,14 +2699,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44566</v>
+        <v>44930</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2723,13 +2718,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2762,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 65095-2021</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2782,14 +2772,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44515</v>
+        <v>44929</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2792,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2845,7 +2835,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61986-2021</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2859,10 +2849,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44502</v>
+        <v>45229</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2874,13 +2864,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2923,7 +2908,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 495-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,10 +2922,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>44566</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2952,8 +2937,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2996,7 +2986,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 496-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3010,10 +3000,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44715</v>
+        <v>44566</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3025,8 +3015,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3069,7 +3064,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45191</v>
+        <v>45719</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3094,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3137,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 61986-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,10 +3151,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45107</v>
+        <v>44502</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3171,8 +3166,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44900</v>
+        <v>44515</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3298,14 +3298,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45021</v>
+        <v>45253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44986</v>
+        <v>45401</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3390,13 +3390,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3439,7 +3434,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3453,10 +3448,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44960</v>
+        <v>44979</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3469,7 +3464,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3512,7 +3507,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3522,14 +3517,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44929</v>
+        <v>45617</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3542,7 +3537,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3585,7 +3580,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3595,14 +3590,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44929</v>
+        <v>45249</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3615,7 +3610,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3658,7 +3653,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3668,14 +3663,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44929</v>
+        <v>45680</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3688,7 +3683,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3731,7 +3726,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3741,14 +3736,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44930</v>
+        <v>45757</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3761,7 +3756,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3804,7 +3799,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3818,10 +3813,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44805</v>
+        <v>45789</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3834,7 +3829,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3877,7 +3872,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3891,10 +3886,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44922</v>
+        <v>45754</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3907,7 +3902,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3950,7 +3945,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3964,10 +3959,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45642</v>
+        <v>45709</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3980,7 +3975,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4023,7 +4018,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4037,10 +4032,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45898</v>
+        <v>45203</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4053,7 +4048,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4096,7 +4091,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4106,14 +4101,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45394</v>
+        <v>45229</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4126,7 +4121,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4169,7 +4164,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4186,7 +4181,7 @@
         <v>45229</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4199,7 +4194,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4242,7 +4237,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4256,10 +4251,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45820</v>
+        <v>45666</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4272,7 +4267,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.8</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4315,7 +4310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4329,10 +4324,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45338</v>
+        <v>45580</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4388,7 +4383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45527</v>
+        <v>45579</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4418,7 +4413,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4478,7 +4473,7 @@
         <v>44901</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4534,7 +4529,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4548,10 +4543,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44922</v>
+        <v>45720</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4564,7 +4559,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4607,7 +4602,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4621,10 +4616,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44502</v>
+        <v>45642</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4636,13 +4631,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4685,7 +4675,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4699,10 +4689,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45203</v>
+        <v>45898</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4715,7 +4705,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4758,7 +4748,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4772,10 +4762,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44944</v>
+        <v>45527</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4788,7 +4778,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4831,7 +4821,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4845,10 +4835,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46112</v>
+        <v>45338</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4861,7 +4851,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4904,7 +4894,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4918,10 +4908,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45525</v>
+        <v>44965</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4934,7 +4924,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4977,7 +4967,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4991,10 +4981,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45960</v>
+        <v>45239</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5007,7 +4997,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5050,7 +5040,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5064,10 +5054,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46125</v>
+        <v>44944</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5080,7 +5070,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5123,7 +5113,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5137,10 +5127,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44979</v>
+        <v>45527</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5153,7 +5143,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5196,7 +5186,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5210,10 +5200,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45799</v>
+        <v>44502</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5225,8 +5215,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5269,7 +5264,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5283,10 +5278,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45754</v>
+        <v>45820</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5299,7 +5294,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>7.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5342,7 +5337,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5356,10 +5351,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45401</v>
+        <v>44922</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5372,7 +5367,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5415,7 +5410,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5425,14 +5420,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45786</v>
+        <v>44929</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5444,13 +5439,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5493,7 +5483,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5503,14 +5493,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45561</v>
+        <v>45203</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5523,7 +5513,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5566,7 +5556,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5580,10 +5570,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45642</v>
+        <v>45519</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5596,7 +5586,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5639,7 +5629,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5653,10 +5643,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45280</v>
+        <v>45063</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5669,7 +5659,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5712,7 +5702,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5726,10 +5716,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46000</v>
+        <v>44574</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5742,7 +5732,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5785,7 +5775,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5795,14 +5785,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46002</v>
+        <v>45021</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5815,7 +5805,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5858,7 +5848,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5872,10 +5862,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46146</v>
+        <v>45558</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5888,7 +5878,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5931,7 +5921,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5945,10 +5935,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45965</v>
+        <v>45960</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5961,7 +5951,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6004,7 +5994,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6018,10 +6008,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44991</v>
+        <v>45525</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6034,7 +6024,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6077,7 +6067,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6087,14 +6077,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44984</v>
+        <v>45194</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6107,7 +6097,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6150,7 +6140,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6164,10 +6154,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45610</v>
+        <v>44922</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6180,7 +6170,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6223,7 +6213,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6237,10 +6227,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45249</v>
+        <v>44986</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6252,8 +6242,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6296,7 +6291,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45754</v>
+        <v>45786</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6325,8 +6320,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6369,7 +6369,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46195</v>
+        <v>45642</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6442,7 +6442,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6452,14 +6452,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45229</v>
+        <v>45619</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6515,7 +6515,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45166</v>
+        <v>46146</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45239</v>
+        <v>45775</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6661,7 +6661,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45932</v>
+        <v>45561</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45527</v>
+        <v>44960</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45324</v>
+        <v>45034</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44965</v>
+        <v>46002</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45558</v>
+        <v>45965</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45063</v>
+        <v>44900</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45194</v>
+        <v>44715</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45519</v>
+        <v>45610</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46273</v>
+        <v>45177</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45775</v>
+        <v>45166</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44845</v>
+        <v>44805</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46281</v>
+        <v>46195</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7537,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45034</v>
+        <v>44953</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7610,7 +7610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7620,14 +7620,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46281</v>
+        <v>44953</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7683,7 +7683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46281</v>
+        <v>45191</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46281</v>
+        <v>44755</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7829,7 +7829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44515</v>
+        <v>45591</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7902,7 +7902,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7916,10 +7916,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46282</v>
+        <v>44602</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44922</v>
+        <v>45107</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8048,7 +8048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8062,10 +8062,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46286</v>
+        <v>44922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8121,7 +8121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8131,14 +8131,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44574</v>
+        <v>45049</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46058</v>
+        <v>46112</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45253</v>
+        <v>44922</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8350,14 +8350,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45580</v>
+        <v>44929</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8413,7 +8413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45757</v>
+        <v>44991</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 40535-2026</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46295</v>
+        <v>46125</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8573,10 +8573,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45049</v>
+        <v>45932</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 41576-2026</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8642,14 +8642,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46301</v>
+        <v>45394</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8715,14 +8715,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45203</v>
+        <v>45324</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8792,10 +8792,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44602</v>
+        <v>45754</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45251</v>
+        <v>46000</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8934,14 +8934,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44755</v>
+        <v>44984</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45591</v>
+        <v>45799</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9080,14 +9080,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45619</v>
+        <v>44845</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9157,10 +9157,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45719</v>
+        <v>45280</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9226,14 +9226,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44953</v>
+        <v>46273</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9299,14 +9299,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44953</v>
+        <v>45251</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45229</v>
+        <v>46281</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45177</v>
+        <v>46281</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45680</v>
+        <v>46282</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45617</v>
+        <v>46281</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45666</v>
+        <v>46281</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45789</v>
+        <v>46286</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9800,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45579</v>
+        <v>46058</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9873,7 +9873,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 40535-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9887,10 +9887,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45709</v>
+        <v>46295</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -9946,7 +9946,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 41576-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9960,10 +9960,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45720</v>
+        <v>46301</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10019,148 +10019,294 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
+          <t>A 41661-2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="E126" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127" ht="15" customHeight="1">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>A 41662-2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="E127" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128" ht="15" customHeight="1">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>S 3071-2022</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>44715</v>
+      </c>
+      <c r="E128" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>S 3719-2023</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D126" s="1" t="n">
+      <c r="D129" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E126" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I126" t="n">
+      <c r="E129" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
         <v>0.4</v>
       </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>S 3071-2022</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D127" s="1" t="n">
-        <v>44715</v>
-      </c>
-      <c r="E127" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I127" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" t="n">
-        <v>0</v>
-      </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" s="2" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 2764-2023</t>
+          <t>A 417-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44944</v>
+        <v>44929</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -855,10 +855,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 2764-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Ask
 Vårstarr</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 417-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 29819-2025</t>
+          <t>A 56101-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45825</v>
+        <v>45973</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1299,361 +1299,361 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 2763-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44944</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 31382-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 29819-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45825</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Nattskärra</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 56101-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 2763-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 31382-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44602</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44623</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44715</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44515</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44804</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44574</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44851</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 65095-2021</t>
+          <t>A 495-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44515</v>
+        <v>44566</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2645,8 +2645,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2689,7 +2694,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 496-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2699,14 +2704,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44930</v>
+        <v>44566</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2718,8 +2723,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2762,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 65095-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2772,14 +2782,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44929</v>
+        <v>44515</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2792,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2835,7 +2845,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 61986-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2849,10 +2859,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45229</v>
+        <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2864,8 +2874,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2908,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 495-2022</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2922,10 +2937,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44566</v>
+        <v>44922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2937,13 +2952,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2986,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 496-2022</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3000,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44566</v>
+        <v>45107</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3015,13 +3025,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3064,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45719</v>
+        <v>45191</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3094,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3137,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61986-2021</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3151,10 +3156,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44502</v>
+        <v>44900</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3166,13 +3171,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44515</v>
+        <v>45021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45253</v>
+        <v>44715</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45401</v>
+        <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3390,8 +3390,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3434,7 +3439,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8969-2023</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3448,10 +3453,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44979</v>
+        <v>44960</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3464,7 +3469,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3507,7 +3512,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3517,14 +3522,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45617</v>
+        <v>44929</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3537,7 +3542,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3580,7 +3585,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3590,14 +3595,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45249</v>
+        <v>44929</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3610,7 +3615,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3653,7 +3658,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3663,14 +3668,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45680</v>
+        <v>44929</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3683,7 +3688,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3726,7 +3731,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3736,14 +3741,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45757</v>
+        <v>44930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3756,7 +3761,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3799,7 +3804,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3813,10 +3818,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45789</v>
+        <v>44805</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3829,7 +3834,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3872,7 +3877,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3886,10 +3891,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45754</v>
+        <v>44922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3902,7 +3907,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3945,7 +3950,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3955,14 +3960,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45709</v>
+        <v>45394</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3975,7 +3980,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4018,7 +4023,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4028,14 +4033,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45203</v>
+        <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4048,7 +4053,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4091,7 +4096,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4105,10 +4110,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45229</v>
+        <v>45338</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4121,7 +4126,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4164,7 +4169,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4178,10 +4183,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45229</v>
+        <v>45527</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4194,7 +4199,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4237,7 +4242,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4251,10 +4256,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45666</v>
+        <v>44901</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4267,7 +4272,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4310,7 +4315,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4324,10 +4329,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45580</v>
+        <v>45525</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4340,7 +4345,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4383,7 +4388,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45579</v>
+        <v>45642</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4413,7 +4418,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4456,7 +4461,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4470,10 +4475,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44901</v>
+        <v>44922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4486,7 +4491,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4529,7 +4534,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4543,10 +4548,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45720</v>
+        <v>44502</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4558,8 +4563,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4602,7 +4612,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4612,14 +4622,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45642</v>
+        <v>45203</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4632,7 +4642,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4675,7 +4685,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4685,14 +4695,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45898</v>
+        <v>44944</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4705,7 +4715,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4748,7 +4758,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4758,14 +4768,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45527</v>
+        <v>45898</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4778,7 +4788,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4821,7 +4831,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 8969-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4835,10 +4845,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45338</v>
+        <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4851,7 +4861,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4894,7 +4904,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4908,10 +4918,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44965</v>
+        <v>45401</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4924,7 +4934,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4967,7 +4977,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4981,10 +4991,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45239</v>
+        <v>45561</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4997,7 +5007,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5040,7 +5050,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5054,10 +5064,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44944</v>
+        <v>46112</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5070,7 +5080,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5113,7 +5123,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5127,10 +5137,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45527</v>
+        <v>44991</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5143,7 +5153,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5186,7 +5196,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5196,14 +5206,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44502</v>
+        <v>44984</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5215,13 +5225,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5264,7 +5269,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5278,10 +5283,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45820</v>
+        <v>45610</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5294,7 +5299,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5337,7 +5342,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5351,10 +5356,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44922</v>
+        <v>45960</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5367,7 +5372,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5410,7 +5415,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5420,14 +5425,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44929</v>
+        <v>45249</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5440,7 +5445,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5483,7 +5488,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5493,14 +5498,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45203</v>
+        <v>46125</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5556,7 +5561,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5570,10 +5575,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45519</v>
+        <v>45754</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5586,7 +5591,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5629,7 +5634,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5643,10 +5648,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45063</v>
+        <v>45229</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5659,7 +5664,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5702,7 +5707,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5716,10 +5721,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44574</v>
+        <v>45799</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5732,7 +5737,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5775,7 +5780,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5785,14 +5790,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45021</v>
+        <v>45754</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5805,7 +5810,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5848,7 +5853,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5862,10 +5867,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45558</v>
+        <v>45786</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5877,8 +5882,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5921,7 +5931,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5935,10 +5945,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45960</v>
+        <v>45166</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5951,7 +5961,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5994,7 +6004,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6008,10 +6018,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45525</v>
+        <v>46002</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6024,7 +6034,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6067,7 +6077,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6081,10 +6091,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45194</v>
+        <v>45239</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6097,7 +6107,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6140,7 +6150,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6154,10 +6164,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44922</v>
+        <v>45642</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6170,7 +6180,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6213,7 +6223,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6227,10 +6237,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44986</v>
+        <v>45280</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6242,13 +6252,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6291,7 +6296,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6305,10 +6310,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45786</v>
+        <v>45527</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6320,13 +6325,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6369,7 +6369,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45642</v>
+        <v>46000</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6442,7 +6442,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6452,14 +6452,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45619</v>
+        <v>45324</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6515,7 +6515,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46146</v>
+        <v>44965</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45775</v>
+        <v>45558</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6661,7 +6661,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45561</v>
+        <v>45063</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44960</v>
+        <v>45194</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45034</v>
+        <v>46146</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46002</v>
+        <v>45519</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45965</v>
+        <v>45775</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44900</v>
+        <v>44845</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7109,14 +7109,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44715</v>
+        <v>45034</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45610</v>
+        <v>44515</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45177</v>
+        <v>44922</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45166</v>
+        <v>45965</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44805</v>
+        <v>44574</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46195</v>
+        <v>45253</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7537,7 +7537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7547,14 +7547,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44953</v>
+        <v>45580</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7610,7 +7610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7620,14 +7620,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44953</v>
+        <v>45757</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7683,7 +7683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7693,14 +7693,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45191</v>
+        <v>45049</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44755</v>
+        <v>46195</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7829,7 +7829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7839,14 +7839,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45591</v>
+        <v>45203</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7919,7 +7919,7 @@
         <v>44602</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45107</v>
+        <v>45251</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8048,7 +8048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8062,10 +8062,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44922</v>
+        <v>44755</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8121,7 +8121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45049</v>
+        <v>45932</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46112</v>
+        <v>45591</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8277,14 +8277,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44922</v>
+        <v>45619</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8350,14 +8350,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44929</v>
+        <v>45719</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8413,7 +8413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8423,14 +8423,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44991</v>
+        <v>44953</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8496,14 +8496,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46125</v>
+        <v>44953</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8569,14 +8569,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45932</v>
+        <v>46273</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8642,14 +8642,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45394</v>
+        <v>45229</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45324</v>
+        <v>45177</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8792,10 +8792,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45754</v>
+        <v>46281</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46000</v>
+        <v>46281</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8934,14 +8934,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44984</v>
+        <v>46281</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45799</v>
+        <v>46281</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44845</v>
+        <v>45680</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9157,10 +9157,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45280</v>
+        <v>45617</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46273</v>
+        <v>46282</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45251</v>
+        <v>45666</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46281</v>
+        <v>45789</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46281</v>
+        <v>45579</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>6.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46282</v>
+        <v>45709</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46281</v>
+        <v>45720</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46286</v>
+        <v>46058</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9800,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46058</v>
+        <v>45820</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>7.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9890,7 +9890,7 @@
         <v>46295</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>46301</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>46301</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>46301</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10179,10 +10179,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10238,7 +10238,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 417-2023</t>
+          <t>A 2764-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44929</v>
+        <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -871,149 +871,149 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
+          <t>Ask
+Vårstarr</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 417-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>Nattskärra
 Huggorm</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 417-2023 artfynd.xlsx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 417-2023 karta.png", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 417-2023 georefererad karta.tif", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 417-2023 FSC-klagomål.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 417-2023 FSC-klagomål mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 417-2023 tillsynsbegäran.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 417-2023 tillsynsbegäran mail.docx", "A 417-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 417-2023 prioriterade fågelarter.docx", "A 417-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 2764-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>44944</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vårstarr</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2764-2023 artfynd.xlsx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2764-2023 karta.png", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2764-2023 georefererad karta.tif", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2764-2023 FSC-klagomål.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2764-2023 FSC-klagomål mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2764-2023 tillsynsbegäran.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2764-2023 tillsynsbegäran mail.docx", "A 2764-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 56101-2025</t>
+          <t>A 29819-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45973</v>
+        <v>45825</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1299,361 +1299,361 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 56101-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>Hasselticka</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 56101-2025 artfynd.xlsx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 56101-2025 karta.png", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 56101-2025 georefererad karta.tif", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 56101-2025 FSC-klagomål.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 56101-2025 FSC-klagomål mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 56101-2025 tillsynsbegäran.docx", "A 56101-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 56101-2025 tillsynsbegäran mail.docx", "A 56101-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 2763-2023</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>44944</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>2.5</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 2763-2023 artfynd.xlsx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 2763-2023 karta.png", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 2763-2023 georefererad karta.tif", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 2763-2023 FSC-klagomål.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 2763-2023 FSC-klagomål mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 2763-2023 tillsynsbegäran.docx", "A 2763-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 2763-2023 tillsynsbegäran mail.docx", "A 2763-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 31382-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46219</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TIBRO</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>1.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 31382-2026 artfynd.xlsx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 31382-2026 karta.png", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 31382-2026 georefererad karta.tif", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 31382-2026 FSC-klagomål.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 31382-2026 FSC-klagomål mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 31382-2026 tillsynsbegäran.docx", "A 31382-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 31382-2026 tillsynsbegäran mail.docx", "A 31382-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 29819-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45825</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/artfynd/A 29819-2025 artfynd.xlsx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor/A 29819-2025 karta.png", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/kartor_geotiff/A 29819-2025 georefererad karta.tif", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomål/A 29819-2025 FSC-klagomål.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/klagomålsmail/A 29819-2025 FSC-klagomål mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsyn/A 29819-2025 tillsynsbegäran.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/tillsynsmail/A 29819-2025 tillsynsbegäran mail.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1472/fåglar/A 29819-2025 prioriterade fågelarter.docx", "A 29819-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6822-2022</t>
+          <t>A 10328-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44602</v>
+        <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10328-2022</t>
+          <t>A 6822-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44623</v>
+        <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23080-2022</t>
+          <t>A 65095-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44715</v>
+        <v>44515</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 65112-2021</t>
+          <t>A 23080-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44515</v>
+        <v>44715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2392,7 +2392,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 36404-2022</t>
+          <t>A 65112-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44804</v>
+        <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2419,11 +2419,6 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>TIBRO</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -2470,7 +2465,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1882-2022</t>
+          <t>A 495-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2484,10 +2479,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44574</v>
+        <v>44566</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2499,8 +2494,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46707-2022</t>
+          <t>A 496-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44851</v>
+        <v>44566</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2572,8 +2572,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2616,7 +2621,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 495-2022</t>
+          <t>A 36404-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2630,10 +2635,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44566</v>
+        <v>44804</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2651,7 +2656,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2694,7 +2699,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 496-2022</t>
+          <t>A 1882-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2708,10 +2713,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44566</v>
+        <v>44574</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2723,13 +2728,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2772,7 +2772,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 65095-2021</t>
+          <t>A 46707-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44515</v>
+        <v>44851</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62220-2022</t>
+          <t>A 17611-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44922</v>
+        <v>45757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29822-2023</t>
+          <t>A 16618-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45107</v>
+        <v>45754</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45054-2023</t>
+          <t>A 47650-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45191</v>
+        <v>45203</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58150-2022</t>
+          <t>A 53160-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44900</v>
+        <v>45229</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15684-2023</t>
+          <t>A 53253-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45021</v>
+        <v>45229</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22789-2022</t>
+          <t>A 53179-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44715</v>
+        <v>45229</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10115-2023</t>
+          <t>A 45881-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44986</v>
+        <v>45580</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3390,13 +3390,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3439,7 +3434,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5564-2023</t>
+          <t>A 14383-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3449,14 +3444,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44960</v>
+        <v>45394</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3469,7 +3464,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3512,7 +3507,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 418-2023</t>
+          <t>A 4316-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3522,14 +3517,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44929</v>
+        <v>45324</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3542,7 +3537,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3585,7 +3580,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 419-2023</t>
+          <t>A 65114-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3595,14 +3590,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44929</v>
+        <v>44515</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3615,7 +3610,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3658,7 +3653,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 420-2023</t>
+          <t>A 58365-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3668,14 +3663,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44929</v>
+        <v>44901</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3688,7 +3683,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3731,7 +3726,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 506-2023</t>
+          <t>A 10737-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3745,10 +3740,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44930</v>
+        <v>44984</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3761,7 +3756,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3804,7 +3799,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 36868-2022</t>
+          <t>A 15409-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3818,10 +3813,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44805</v>
+        <v>45401</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3834,7 +3829,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3877,7 +3872,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62221-2022</t>
+          <t>A 45588-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3891,10 +3886,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44922</v>
+        <v>44845</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3907,7 +3902,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3950,7 +3945,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 14383-2024</t>
+          <t>A 35048-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3960,14 +3955,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45394</v>
+        <v>45527</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3980,7 +3975,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4023,7 +4018,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 53160-2023</t>
+          <t>A 6355-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4037,10 +4032,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45229</v>
+        <v>45338</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4053,7 +4048,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4096,7 +4091,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 6355-2024</t>
+          <t>A 7179-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4110,10 +4105,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45338</v>
+        <v>44965</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4126,7 +4121,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4169,7 +4164,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35055-2024</t>
+          <t>A 55788-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4183,10 +4178,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45527</v>
+        <v>45239</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4199,7 +4194,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4242,7 +4237,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 58365-2022</t>
+          <t>A 58633-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4256,10 +4251,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44901</v>
+        <v>45251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4272,7 +4267,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4315,7 +4310,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34530-2024</t>
+          <t>A 35055-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4329,10 +4324,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45525</v>
+        <v>45527</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4345,7 +4340,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4388,7 +4383,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60264-2024</t>
+          <t>A 61975-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45642</v>
+        <v>44502</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4417,8 +4412,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62219-2022</t>
+          <t>A 2761-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44922</v>
+        <v>44944</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61975-2021</t>
+          <t>A 60264-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44502</v>
+        <v>45642</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4563,13 +4563,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4612,7 +4607,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47649-2023</t>
+          <t>A 41130-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4626,10 +4621,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45203</v>
+        <v>45898</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4642,7 +4637,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4685,7 +4680,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2761-2023</t>
+          <t>A 62219-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4699,10 +4694,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44944</v>
+        <v>44922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4715,7 +4710,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4758,7 +4753,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 41130-2025</t>
+          <t>A 59273-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4768,14 +4763,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45898</v>
+        <v>45253</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4788,7 +4783,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4848,7 +4843,7 @@
         <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4904,7 +4899,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15409-2024</t>
+          <t>A 419-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4914,14 +4909,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45401</v>
+        <v>44929</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4934,7 +4929,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4977,7 +4972,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 41931-2024</t>
+          <t>A 54412-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4991,10 +4986,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45561</v>
+        <v>45617</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5007,7 +5002,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5050,7 +5045,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16586-2026</t>
+          <t>A 47649-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5060,14 +5055,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46112</v>
+        <v>45203</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5080,7 +5075,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5123,7 +5118,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10836-2023</t>
+          <t>A 33522-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5137,10 +5132,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44991</v>
+        <v>45519</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5153,7 +5148,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5196,7 +5191,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10737-2023</t>
+          <t>A 3572-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5206,14 +5201,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44984</v>
+        <v>45680</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5226,7 +5221,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5269,7 +5264,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52631-2024</t>
+          <t>A 21738-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5283,10 +5278,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45610</v>
+        <v>45063</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5299,7 +5294,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5342,7 +5337,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 53651-2025</t>
+          <t>A 1878-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5356,10 +5351,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45960</v>
+        <v>44574</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5372,7 +5367,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5415,7 +5410,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58101-2023</t>
+          <t>A 40671-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5429,10 +5424,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45249</v>
+        <v>45558</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5445,7 +5440,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.1</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5488,7 +5483,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18004-2026</t>
+          <t>A 22828-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5502,10 +5497,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46125</v>
+        <v>45789</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5561,7 +5556,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16618-2025</t>
+          <t>A 15684-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5571,14 +5566,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45754</v>
+        <v>45021</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5591,7 +5586,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5634,7 +5629,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53253-2023</t>
+          <t>A 8450-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5648,10 +5643,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45229</v>
+        <v>45709</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5664,7 +5659,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5707,7 +5702,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25063-2025</t>
+          <t>A 1191-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5721,10 +5716,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45799</v>
+        <v>45666</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5737,7 +5732,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5780,7 +5775,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16687-2025</t>
+          <t>A 45599-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5794,10 +5789,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45754</v>
+        <v>45579</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5810,7 +5805,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5853,7 +5848,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22418-2025</t>
+          <t>A 10462-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5867,10 +5862,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45786</v>
+        <v>45720</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5882,13 +5877,8 @@
           <t>TIBRO</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5931,7 +5921,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39459-2023</t>
+          <t>A 62223-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5945,10 +5935,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45166</v>
+        <v>44922</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5961,7 +5951,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6004,7 +5994,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 61701-2025</t>
+          <t>A 10115-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6018,10 +6008,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46002</v>
+        <v>44986</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6033,8 +6023,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6077,7 +6072,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 55788-2023</t>
+          <t>A 45669-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6091,10 +6086,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45239</v>
+        <v>45194</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6107,7 +6102,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6150,7 +6145,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60259-2024</t>
+          <t>A 54948-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6160,14 +6155,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45642</v>
+        <v>45619</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6180,7 +6175,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6223,7 +6218,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64438-2023</t>
+          <t>A 28703-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6237,10 +6232,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45280</v>
+        <v>45820</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6253,7 +6248,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6296,7 +6291,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35048-2024</t>
+          <t>A 20430-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6310,10 +6305,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45527</v>
+        <v>45775</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6326,7 +6321,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6369,7 +6364,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61133-2025</t>
+          <t>A 41931-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6383,10 +6378,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46000</v>
+        <v>45561</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6399,7 +6394,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6442,7 +6437,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 4316-2024</t>
+          <t>A 5564-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6456,10 +6451,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45324</v>
+        <v>44960</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6472,7 +6467,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6515,7 +6510,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7179-2023</t>
+          <t>A 17150-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6525,14 +6520,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44965</v>
+        <v>45034</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6545,7 +6540,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6588,7 +6583,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40671-2024</t>
+          <t>A 53651-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6602,10 +6597,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45558</v>
+        <v>45960</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6618,7 +6613,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6661,7 +6656,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21738-2023</t>
+          <t>A 58150-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6675,10 +6670,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45063</v>
+        <v>44900</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6691,7 +6686,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6734,7 +6729,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 45669-2023</t>
+          <t>A 22789-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6748,10 +6743,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45194</v>
+        <v>44715</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6764,7 +6759,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6807,7 +6802,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21403-2026</t>
+          <t>A 52631-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6821,10 +6816,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46146</v>
+        <v>45610</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6837,7 +6832,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6880,7 +6875,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33522-2024</t>
+          <t>A 42016-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6894,10 +6889,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45519</v>
+        <v>45177</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6910,7 +6905,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6953,7 +6948,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 20430-2025</t>
+          <t>A 506-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6963,14 +6958,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45775</v>
+        <v>44930</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6983,7 +6978,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7026,7 +7021,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45588-2022</t>
+          <t>A 420-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7036,14 +7031,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44845</v>
+        <v>44929</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7056,7 +7051,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7099,7 +7094,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17150-2023</t>
+          <t>A 34530-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7109,14 +7104,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45034</v>
+        <v>45525</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7129,7 +7124,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7172,7 +7167,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 65114-2021</t>
+          <t>A 9954-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7186,10 +7181,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44515</v>
+        <v>45719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7202,7 +7197,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7245,7 +7240,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 62223-2022</t>
+          <t>A 58101-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7259,10 +7254,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44922</v>
+        <v>45249</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7275,7 +7270,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>6.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7318,7 +7313,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 54449-2025</t>
+          <t>A 39459-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7332,10 +7327,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45965</v>
+        <v>45166</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7348,7 +7343,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7391,7 +7386,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1878-2022</t>
+          <t>A 16586-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7405,10 +7400,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44574</v>
+        <v>46112</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7421,7 +7416,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7464,7 +7459,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59273-2023</t>
+          <t>A 18004-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7478,10 +7473,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45253</v>
+        <v>46125</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7494,7 +7489,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7537,7 +7532,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 45881-2024</t>
+          <t>A 36868-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7551,10 +7546,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45580</v>
+        <v>44805</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7567,7 +7562,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7610,7 +7605,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 17611-2025</t>
+          <t>A 61701-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7624,10 +7619,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45757</v>
+        <v>46002</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7640,7 +7635,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7683,7 +7678,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19384-2023</t>
+          <t>A 4241-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7697,10 +7692,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45049</v>
+        <v>44953</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7713,7 +7708,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7756,7 +7751,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 27990-2026</t>
+          <t>A 4242-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7766,14 +7761,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46195</v>
+        <v>44953</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7829,7 +7824,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 47650-2023</t>
+          <t>A 45054-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7839,14 +7834,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45203</v>
+        <v>45191</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7859,7 +7854,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7902,7 +7897,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 6872-2022</t>
+          <t>A 29728-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7916,10 +7911,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44602</v>
+        <v>44755</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7932,7 +7927,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7975,7 +7970,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 58633-2023</t>
+          <t>A 48510-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7989,10 +7984,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45251</v>
+        <v>45591</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8005,7 +8000,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8048,7 +8043,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 29728-2022</t>
+          <t>A 16687-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8062,10 +8057,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44755</v>
+        <v>45754</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8078,7 +8073,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8121,7 +8116,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 47903-2025</t>
+          <t>A 6872-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8131,14 +8126,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45932</v>
+        <v>44602</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8151,7 +8146,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8194,7 +8189,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48510-2024</t>
+          <t>A 61133-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8208,10 +8203,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45591</v>
+        <v>46000</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8224,7 +8219,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8267,7 +8262,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 54948-2024</t>
+          <t>A 25063-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8277,14 +8272,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45619</v>
+        <v>45799</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8297,7 +8292,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8340,7 +8335,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 9954-2025</t>
+          <t>A 29822-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8354,10 +8349,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45719</v>
+        <v>45107</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8370,7 +8365,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8413,7 +8408,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4241-2023</t>
+          <t>A 64438-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8423,14 +8418,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44953</v>
+        <v>45280</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8443,7 +8438,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8486,7 +8481,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 4242-2023</t>
+          <t>A 62221-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8496,14 +8491,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44953</v>
+        <v>44922</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8516,7 +8511,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8559,7 +8554,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 37090-2026</t>
+          <t>A 22418-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8573,10 +8568,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46273</v>
+        <v>45786</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8588,8 +8583,13 @@
           <t>TIBRO</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 53179-2023</t>
+          <t>A 60259-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45229</v>
+        <v>45642</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 42016-2023</t>
+          <t>A 19384-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8715,14 +8715,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45177</v>
+        <v>45049</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 38203-2026</t>
+          <t>A 62220-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8792,10 +8792,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46281</v>
+        <v>44922</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 38196-2026</t>
+          <t>A 418-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8861,14 +8861,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46281</v>
+        <v>44929</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 38202-2026</t>
+          <t>A 10836-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46281</v>
+        <v>44991</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 38205-2026</t>
+          <t>A 21403-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46281</v>
+        <v>46146</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9070,7 +9070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 3572-2025</t>
+          <t>A 54449-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45680</v>
+        <v>45965</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 54412-2024</t>
+          <t>A 27990-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9157,10 +9157,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45617</v>
+        <v>46195</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9216,7 +9216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 38488-2026</t>
+          <t>A 47903-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9226,14 +9226,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46282</v>
+        <v>45932</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 1191-2025</t>
+          <t>A 37090-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45666</v>
+        <v>46273</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9362,7 +9362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 22828-2025</t>
+          <t>A 38202-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45789</v>
+        <v>46281</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9435,7 +9435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 45599-2024</t>
+          <t>A 38205-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45579</v>
+        <v>46281</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9508,7 +9508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 8450-2025</t>
+          <t>A 38488-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9522,10 +9522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45709</v>
+        <v>46282</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9581,7 +9581,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38813-2026</t>
+          <t>A 38196-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9595,10 +9595,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9654,7 +9654,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 10462-2025</t>
+          <t>A 38203-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9668,10 +9668,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45720</v>
+        <v>46281</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9727,7 +9727,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 7310-2026</t>
+          <t>A 38813-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9741,10 +9741,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46058</v>
+        <v>46286</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9800,7 +9800,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 28703-2025</t>
+          <t>A 7310-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45820</v>
+        <v>46058</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>7.8</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9890,7 +9890,7 @@
         <v>46295</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>46301</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>46301</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>46301</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>S 3719-2023</t>
+          <t>S 3071-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10179,10 +10179,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45222</v>
+        <v>44715</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10238,7 +10238,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>S 3071-2022</t>
+          <t>S 3719-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44715</v>
+        <v>45222</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>

--- a/Översikt TIBRO.xlsx
+++ b/Översikt TIBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45590</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>44944</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44929</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>44755</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45825</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>45973</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>44944</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>46219</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>44734</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>44602</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>44602</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44623</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>44602</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44804</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>44512</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44515</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44715</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>44515</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>44566</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44566</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>44804</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>44574</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>44851</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44502</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>45757</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45754</v>
       </c>
       <c r="E30" s="1" t="n">
